--- a/workspaces/btc_daily_14days/ma/ma_ratio_30.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_30.xlsx
@@ -575,46 +575,46 @@
         <v>20</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.493438320209975</v>
+        <v>-7.469722005690187</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>15.89888096196837</v>
+        <v>15.84827332511004</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.50528985843619</v>
+        <v>10.47168162009518</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.634548205620433</v>
+        <v>5.616453450224135</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.1067926473101</v>
+        <v>15.05855819629772</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.40200689687256</v>
+        <v>10.36921132525779</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.31963427599701</v>
+        <v>10.28718892411641</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.845354039382798</v>
+        <v>4.83072357946439</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.794943165043016</v>
+        <v>9.764934368367769</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>13.95657612589405</v>
+        <v>13.91291765147245</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.742378326593055</v>
+        <v>8.715363517090694</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.247905427167645</v>
+        <v>-1.243312540864821</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.344742095865968</v>
+        <v>3.334974929834068</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>13.62825930859162</v>
+        <v>13.5854475825754</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>37</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.844789671561323</v>
+        <v>-3.832533342745087</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-8.161101489854062</v>
+        <v>-8.134639955716558</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.258017809995344</v>
+        <v>2.250596805434824</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3.020498633748581</v>
+        <v>-3.010867896020386</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.8548211666307921</v>
+        <v>-0.8521350466731548</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.148679680424905</v>
+        <v>2.142102439133701</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.6424566545899282</v>
+        <v>-0.639921206410051</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.596566785145427</v>
+        <v>1.592232345644575</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.24361974185539</v>
+        <v>4.231133129485798</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.024711465851638</v>
+        <v>-2.017320896344067</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.4788788038829281</v>
+        <v>0.4781971576853437</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-7.616734679592334</v>
+        <v>-7.59148609201916</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.09191915301743592</v>
+        <v>0.09252999489270763</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.368798670516995</v>
+        <v>-2.360498363370546</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>35</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10.36370453693418</v>
+        <v>10.32984245906822</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.896442526023471</v>
+        <v>5.877534556461129</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.361486986209471</v>
+        <v>8.334025988769369</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.35321373186454</v>
+        <v>11.31613979131134</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10.81710848927112</v>
+        <v>10.7817761233045</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>8.256773409421285</v>
+        <v>8.230156333746855</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.4104683559718723</v>
+        <v>-0.4086437195352062</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.740949845984218</v>
+        <v>-3.72795472287639</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.940391070003443</v>
+        <v>-0.9361960204424378</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.934597598538396</v>
+        <v>3.922685885851728</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.458946252933046</v>
+        <v>9.428964567759536</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>20.95593873833987</v>
+        <v>20.88845605242092</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>20.53956775430127</v>
+        <v>20.47350136306192</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>17.92891088429847</v>
+        <v>17.87116186828969</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.474815648043268</v>
+        <v>1.495452492651239</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.899924002913764</v>
+        <v>-4.964350799269667</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.056280927350834</v>
+        <v>1.071758658246303</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.4015934360576168</v>
+        <v>-0.405337598785664</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.940640205028032</v>
+        <v>-0.9514367512517339</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.232530311633219</v>
+        <v>-2.261910959516598</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.040762950091427</v>
+        <v>4.091372986921293</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.163653159241477</v>
+        <v>5.227261276840267</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.875251093403214</v>
+        <v>9.999184236777232</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.434897354095916</v>
+        <v>7.528447774702627</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.048906418040772</v>
+        <v>4.099212663667039</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.492896815778117</v>
+        <v>2.524275304921503</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.256246058660054</v>
+        <v>5.323323048843875</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.221785115572636</v>
+        <v>3.26286693741411</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>68</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.859502856260278</v>
+        <v>4.843954056863637</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.661648326827581</v>
+        <v>7.638195795033759</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.325971714582437</v>
+        <v>4.312034059051811</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.98572234305788</v>
+        <v>2.97608764805809</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.919649610772566</v>
+        <v>3.9071428470425</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.273319666473185</v>
+        <v>1.269543242914018</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.607362166301947</v>
+        <v>5.590192124232154</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.194037931781182</v>
+        <v>2.187831093122263</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.6597743299991663</v>
+        <v>0.6583565666309212</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.281970345417484</v>
+        <v>1.278399491109838</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.820638897119203</v>
+        <v>-4.805249093544653</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.787217404126189</v>
+        <v>-4.772177585220085</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.259611322633212</v>
+        <v>-2.252509043818542</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.9412688863286505</v>
+        <v>0.938388759045985</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.532665045185581</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.700429967230015</v>
+        <v>5.799038686291347</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.287906779805226</v>
+        <v>6.400558679014807</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.3446550656787</v>
+        <v>10.52626781993951</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>12.75278233922377</v>
+        <v>12.97609917725794</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>10.10869143248647</v>
+        <v>10.28272202114616</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.134808605190308</v>
+        <v>4.206367510499355</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.614211037140876</v>
+        <v>6.725668827248043</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.537222402840293</v>
+        <v>7.664089782051043</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.174780222915757</v>
+        <v>-1.197063491697989</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.568352887122835</v>
+        <v>1.591818770219064</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.774842781790888</v>
+        <v>-1.807754830743391</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.617954133191681</v>
+        <v>-2.664273749700889</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5754966895841562</v>
+        <v>0.5854475825753909</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.273926125087655</v>
+        <v>-1.280261004950972</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-6.13917929150626</v>
+        <v>-6.173240476624066</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.908864719218187</v>
+        <v>-4.93450847474351</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-6.407071339666224</v>
+        <v>-6.441011254739756</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4364116648592145</v>
+        <v>-0.4359342495152561</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.6751996966264713</v>
+        <v>0.6803848157485604</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.404737967272098</v>
+        <v>1.413415065612057</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.009758397602894</v>
+        <v>5.038358322498418</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.135190194592646</v>
+        <v>4.158767023176615</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.468686091089083</v>
+        <v>2.481897826590831</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.093406925502265</v>
+        <v>1.098646884226078</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.127638739342913</v>
+        <v>1.133030041571878</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.9205547881324918</v>
+        <v>-0.9265688316681064</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.11819019682482</v>
+        <v>-3.135863892834436</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.506561679790025</v>
+        <v>1.513732757294051</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.562378941222228</v>
+        <v>2.573460777624788</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.83522875473458</v>
+        <v>2.848817410683118</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.9647510975541138</v>
+        <v>0.9700826831369085</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.765846562871602</v>
+        <v>5.793499666971492</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.250589324894889</v>
+        <v>-2.25931679363029</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.9996967518915767</v>
+        <v>-1.003345238053832</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.800494132020532</v>
+        <v>-2.812014742220079</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.533832720404142</v>
+        <v>-5.557534902471204</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.712646778993758</v>
+        <v>-5.738078501985179</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.238771723290981</v>
+        <v>-1.24484524912171</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.209117763394502</v>
+        <v>-3.223884910568223</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.295640699025164</v>
+        <v>-4.315280461110284</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.047370196967371</v>
+        <v>-4.065559128833996</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.454976781748442</v>
+        <v>-3.567491514877986</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-9.877241096652611</v>
+        <v>-10.21580605111564</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-8.569152247435682</v>
+        <v>-8.85146944674198</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.217226178679702</v>
+        <v>-7.455935970598311</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-9.8995730410184</v>
+        <v>-10.21379845458647</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-9.116745978885817</v>
+        <v>-9.42514170485493</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-10.86090439383378</v>
+        <v>-11.23107907511239</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-12.49576958450036</v>
+        <v>-12.92466311813005</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-10.84285295533603</v>
+        <v>-11.22010294108505</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-12.35272377662524</v>
+        <v>-12.79006688223161</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-12.07367853912329</v>
+        <v>-12.49730776873812</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-11.55645760388163</v>
+        <v>-11.96541217358186</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-11.47946267808887</v>
+        <v>-11.88815434671582</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-14.12676801319166</v>
+        <v>-14.6235076413052</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.9144909517890056</v>
+        <v>-0.9177556176376171</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.983390239073458</v>
+        <v>-1.99233587683613</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.132752179672416</v>
+        <v>-4.147767963714642</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.055559702371553</v>
+        <v>-5.073852859275917</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.189828530974552</v>
+        <v>-4.203823370122741</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3192124134291419</v>
+        <v>0.3189706802689045</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.571680694983755</v>
+        <v>-2.582664445454164</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.790997407790123</v>
+        <v>-4.810411224517274</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.851568217612915</v>
+        <v>-4.871411110699576</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.592246750240946</v>
+        <v>-3.608860239389386</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.498539922343753</v>
+        <v>-4.517838915819731</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.358786338013587</v>
+        <v>-2.370779702136183</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.075570257555668</v>
+        <v>-2.08680896096849</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.475615346836122</v>
+        <v>-1.484974952635866</v>
       </c>
     </row>
     <row r="16">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.2106</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4065~4078</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4065</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.09029952668373653</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.1929</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4045~4058</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4045</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.05381288896305847</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.1753</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4008~4021</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4008</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.01892949156038526</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.1576</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3973~3986</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3973</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.1100966242742061</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.1399</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3911~3923</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3911</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.1355489498301665</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.1222</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3843~3855</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3843</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.2236588130763764</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.1045</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3743~3753</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3743</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.1619701614036799</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.08681</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3621~3630</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3621</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.124292314700341</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.06912</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3472~3480</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3472</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.194587745497337</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.05143</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3271~3272</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3271</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.01267414922767074</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.03374</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2987~2987</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2987</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.1011381779487124</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.01605</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2665~2665</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2665</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.3771057698463096</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.001639</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2284~2284</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2284</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.052971487145548</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.01933</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1935~1935</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1935</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.92516633095282</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.03702</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1616~1616</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1616</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.714482471869239</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.05471</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1338~1338</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1338</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.990866612525451</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.0724</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1109~1109</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1109</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.691412897102914</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.09009</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>904~904</t>
-        </is>
+      <c r="B23" t="n">
+        <v>904</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>2.81629619306436</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.1078</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>753~753</t>
-        </is>
+      <c r="B24" t="n">
+        <v>753</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>3.416256234902903</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.1255</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>638~638</t>
-        </is>
+      <c r="B25" t="n">
+        <v>638</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>4.403113403927961</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.1432</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>534~534</t>
-        </is>
+      <c r="B26" t="n">
+        <v>534</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>3.311805125482913</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.1608</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>435~435</t>
-        </is>
+      <c r="B27" t="n">
+        <v>435</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>3.828400760249792</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.1785</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>369~369</t>
-        </is>
+      <c r="B28" t="n">
+        <v>369</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>3.062117235345582</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.1962</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>303~303</t>
-        </is>
+      <c r="B29" t="n">
+        <v>303</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>2.952106234245477</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.2139</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>234~234</t>
-        </is>
+      <c r="B30" t="n">
+        <v>234</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.352715525943871</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.2316</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>190~190</t>
-        </is>
+      <c r="B31" t="n">
+        <v>190</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.1381406271584424</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.2493</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>148~148</t>
-        </is>
+      <c r="B32" t="n">
+        <v>148</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.8849400581684037</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.267</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>125~125</t>
-        </is>
+      <c r="B33" t="n">
+        <v>125</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>3.506561679790032</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.2847</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>102~102</t>
-        </is>
+      <c r="B34" t="n">
+        <v>102</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>1.428130307241005</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.3024</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>2.268466441694791</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.2106</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>5.83989501312336</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.1929</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>104~104</t>
-        </is>
+      <c r="B7" t="n">
+        <v>104</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>3.275792449020798</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.1753</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>141~141</t>
-        </is>
+      <c r="B8" t="n">
+        <v>141</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.407270899648182</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.1576</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>176~176</t>
-        </is>
+      <c r="B9" t="n">
+        <v>176</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3.188379861608205</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.1399</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>238~239</t>
-        </is>
+      <c r="B10" t="n">
+        <v>238</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>2.736687202802578</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.1222</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>306~307</t>
-        </is>
+      <c r="B11" t="n">
+        <v>306</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>3.206887412689049</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.1045</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>406~409</t>
-        </is>
+      <c r="B12" t="n">
+        <v>406</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.785290286146989</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.08681</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>528~532</t>
-        </is>
+      <c r="B13" t="n">
+        <v>528</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.077990251218594</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.06912</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>677~682</t>
-        </is>
+      <c r="B14" t="n">
+        <v>677</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1.172250829350141</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.05143</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>878~890</t>
-        </is>
+      <c r="B15" t="n">
+        <v>878</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.09083134271136828</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.03374</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1162~1175</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1162</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.1530127882950865</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.01605</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1484~1497</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1484</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.5896307049795197</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.001639</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1865~1878</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1865</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.215483048644472</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.01933</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2214~2227</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2214</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.617820897668445</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.03702</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2533~2546</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2533</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.040178304499051</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.05471</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2811~2824</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2811</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.8999539009465138</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.0724</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3040~3053</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3040</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.9375916120540566</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.09009</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3245~3258</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3245</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.7438987253665132</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.1078</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3396~3409</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3396</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.7187243278368385</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.1255</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3511~3524</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3511</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.7624508060215547</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.1432</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3615~3628</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3615</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.4537470302430506</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.1608</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3714~3727</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3714</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.4140178748115346</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.1785</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3780~3793</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3780</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.2656502896273167</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.1962</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3846~3859</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3846</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.2000980766235614</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.2139</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3915~3928</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3915</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.0494464668494814</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.2316</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3959~3972</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3959</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.02418504333484606</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.2493</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4001~4014</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4001</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.002157802023631916</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.267</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4024~4037</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4024</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.07827854810197721</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.2847</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4047~4060</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4047</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.005753591145932546</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.3024</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4065~4078</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4065</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.01673405341252732</v>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_30.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_30.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-30 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-30 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -572,153 +572,153 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-7.469722005690187</v>
+        <v>-4.846583499326243</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>15.84827332511004</v>
+        <v>17.28548974534039</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.47168162009518</v>
+        <v>12.14679910256503</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.616453450224135</v>
+        <v>7.529464293968957</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.05855819629772</v>
+        <v>16.49703901752626</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.36921132525779</v>
+        <v>12.04560460542365</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.28718892411641</v>
+        <v>11.96401932844195</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4.83072357946439</v>
+        <v>6.745825154996346</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.764934368367769</v>
+        <v>11.44272528411516</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>13.91291765147245</v>
+        <v>15.35346923418861</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.715363517090694</v>
+        <v>10.39424199295348</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.243312540864821</v>
+        <v>0.9119310499563724</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.334974929834068</v>
+        <v>5.252818642849675</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>13.5854475825754</v>
+        <v>15.00358937544868</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.1841</t>
+          <t>X ≈ -0.184</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.832533342745087</v>
+        <v>-5.241909649469676</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-8.134639955716558</v>
+        <v>-9.618830302969812</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.250596805434824</v>
+        <v>1.065623703155104</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3.010867896020386</v>
+        <v>-4.34594090215289</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.8521350466731548</v>
+        <v>-2.112497476288389</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.142102439133701</v>
+        <v>0.9562882399010704</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.639921206410051</v>
+        <v>-1.900949999674495</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.592232345644575</v>
+        <v>0.4059708327257354</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.231133129485798</v>
+        <v>3.11957893025145</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.017320896344067</v>
+        <v>-3.278945087262521</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.4781971576853437</v>
+        <v>-0.7086669765657234</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-7.59148609201916</v>
+        <v>-9.003762261855087</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.09252999489270763</v>
+        <v>-1.094821783788028</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.360498363370546</v>
+        <v>-3.647204275343711</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.1664</t>
+          <t>X ≈ -0.1663</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>35</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10.32984245906822</v>
+        <v>10.34233070128347</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.877534556461129</v>
+        <v>5.89040816202845</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.334025988769369</v>
+        <v>8.347001568672404</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.31613979131134</v>
+        <v>11.32909214463691</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10.7817761233045</v>
+        <v>10.79486219953713</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>8.230156333746855</v>
+        <v>8.243175983035719</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.4086437195352062</v>
+        <v>-0.3956017248950232</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.72795472287639</v>
+        <v>-3.714796024225485</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.9361960204424378</v>
+        <v>-0.92301508318468</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.922685885851728</v>
+        <v>3.936077813848151</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.428964567759536</v>
+        <v>9.442412969672674</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>20.88845605242092</v>
+        <v>20.90190386555788</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>20.47350136306192</v>
+        <v>20.4870551152781</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>17.87116186828969</v>
+        <v>17.86073223259023</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.495452492651239</v>
+        <v>1.482043681729252</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.964350799269667</v>
+        <v>-4.870663019714776</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.071758658246303</v>
+        <v>1.065311568938675</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.405337598785664</v>
+        <v>-0.3876963248379397</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.9514367512517339</v>
+        <v>-0.9248137563875858</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.261910959516598</v>
+        <v>-2.212039236407783</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.091372986921293</v>
+        <v>4.040926128460519</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.227261276840267</v>
+        <v>5.160626502557577</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.999184236777232</v>
+        <v>9.856894168729468</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.528447774702627</v>
+        <v>7.424481348955602</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.099212663667039</v>
+        <v>4.049550668770316</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.524275304921503</v>
+        <v>2.498356366977987</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.323323048843875</v>
+        <v>5.252727727762007</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.26286693741411</v>
+        <v>3.892478264337562</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>68</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.843954056863637</v>
+        <v>4.855139997508104</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.638195795033759</v>
+        <v>7.649114277940868</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.312034059051811</v>
+        <v>4.323843482990263</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.97608764805809</v>
+        <v>2.988230067211859</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.9071428470425</v>
+        <v>3.919181187725854</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.269543242914018</v>
+        <v>1.282243111144538</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.590192124232154</v>
+        <v>5.601804718912511</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.187831093122263</v>
+        <v>2.200473639524027</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.6583565666309212</v>
+        <v>0.6714189205261434</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.278399491109838</v>
+        <v>1.291492428761131</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.805249093544653</v>
+        <v>-4.790521557029109</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.772177585220085</v>
+        <v>-4.757480112602252</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.252509043818542</v>
+        <v>-2.238365064471616</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.938388759045985</v>
+        <v>0.9279591233478328</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>100</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.532665045185581</v>
+        <v>-2.519297082446791</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.799038686291347</v>
+        <v>5.810644421059521</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.400558679014807</v>
+        <v>6.412045649655774</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.52626781993951</v>
+        <v>10.53664774251819</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>12.97609917725794</v>
+        <v>12.98596177061307</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>10.28272202114616</v>
+        <v>10.29329311448015</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.206367510499355</v>
+        <v>4.218574690123738</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.725668827248043</v>
+        <v>6.737370740473807</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.664089782051043</v>
+        <v>7.675571259611473</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.197063491697989</v>
+        <v>-1.18302396201122</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.591818770219064</v>
+        <v>1.605196886617918</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.807754830743391</v>
+        <v>-2.357745003481462</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.664273749700889</v>
+        <v>-3.217835289197168</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5854475825753909</v>
+        <v>0.5750179468772387</v>
       </c>
     </row>
     <row r="12">
@@ -887,98 +887,98 @@
         <v>122</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.280261004950972</v>
+        <v>-1.267355174012643</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-6.173240476624066</v>
+        <v>-6.158592362739341</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.93450847474351</v>
+        <v>-4.920167798763934</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-6.441011254739756</v>
+        <v>-6.426290819705692</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4359342495152561</v>
+        <v>-0.4227519899160015</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.6803848157485604</v>
+        <v>0.6932739999700317</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.413415065612057</v>
+        <v>1.426161923176807</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.038358322498418</v>
+        <v>5.05025456035964</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.158767023176615</v>
+        <v>4.170929615948801</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.481897826590831</v>
+        <v>2.4947779179493</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.098646884226078</v>
+        <v>0.6495060975107378</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.133030041571878</v>
+        <v>1.146482330291988</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.9265688316681064</v>
+        <v>-0.9130127853165035</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.135863892834436</v>
+        <v>-3.146293528532588</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.07797</t>
+          <t>X ≈ -0.07796</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>149</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.513732757294051</v>
+        <v>1.525843742702641</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.573460777624788</v>
+        <v>2.585708785135516</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.848817410683118</v>
+        <v>2.861002392210928</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.9700826831369085</v>
+        <v>0.982785880161849</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.793499666971492</v>
+        <v>5.804872731374942</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.25931679363029</v>
+        <v>-2.610501346167005</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.003345238053832</v>
+        <v>-0.990056536944536</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.812014742220079</v>
+        <v>-2.798089550202675</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.557534902471204</v>
+        <v>-5.54278645954421</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.738078501985179</v>
+        <v>-5.723005179713603</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.24484524912171</v>
+        <v>-1.231387955411492</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.223884910568223</v>
+        <v>-3.210432621848113</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.315280461110284</v>
+        <v>-4.301724414758681</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.065559128833996</v>
+        <v>-4.075988764532148</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>201</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.567491514877986</v>
+        <v>-3.814489791282156</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-10.21580605111564</v>
+        <v>-10.19925849809253</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-8.85146944674198</v>
+        <v>-9.10713237498576</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.455935970598311</v>
+        <v>-7.711495749463033</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-10.21379845458647</v>
+        <v>-10.46952400382421</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-9.42514170485493</v>
+        <v>-9.412098808560565</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-11.23107907511239</v>
+        <v>-11.48914896481414</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-12.92466311813005</v>
+        <v>-13.18534990656182</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-11.22010294108505</v>
+        <v>-11.48193189554286</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-12.79006688223161</v>
+        <v>-13.0571481793509</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-12.49730776873812</v>
+        <v>-12.48385047502791</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-11.96541217358186</v>
+        <v>-11.95195988486175</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-11.88815434671582</v>
+        <v>-11.87459830036421</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-14.6235076413052</v>
+        <v>-14.63393727700335</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>284</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.9177556176376171</v>
+        <v>-0.9052333279619944</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.99233587683613</v>
+        <v>-2.171839717867783</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.147767963714642</v>
+        <v>-4.13476083229704</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.073852859275917</v>
+        <v>-5.060873716877452</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.203823370122741</v>
+        <v>-4.190712565747802</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3189706802689045</v>
+        <v>0.3320135765632699</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.582664445454164</v>
+        <v>-2.569598191153688</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.810411224517274</v>
+        <v>-4.797230215222037</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.871411110699576</v>
+        <v>-4.858212371744813</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.608860239389386</v>
+        <v>-3.595455111736555</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.517838915819731</v>
+        <v>-4.504381622109513</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.370779702136183</v>
+        <v>-2.357327413416073</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.08680896096849</v>
+        <v>-2.073252914616887</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.484974952635866</v>
+        <v>-1.495404588334019</v>
       </c>
     </row>
     <row r="16">
@@ -1095,462 +1095,462 @@
         <v>322</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.182879313998797</v>
+        <v>-2.170357024323174</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.794452926963125</v>
+        <v>-3.781543117387073</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.325967596292493</v>
+        <v>-2.312960464874891</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.437950488529786</v>
+        <v>-3.424971346131322</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5602226352789756</v>
+        <v>-0.5471118309040364</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2627806975632367</v>
+        <v>-0.2497378012688714</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3475144148355938</v>
+        <v>-0.3344481605351177</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.048656223650056</v>
+        <v>1.061837232945294</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.05597931883415441</v>
+        <v>0.06917805778891761</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.104704872405023</v>
+        <v>-1.091299744752192</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6883401843001735</v>
+        <v>-0.6748828905899558</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.3433980207436349</v>
+        <v>-0.3299457320235248</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1680243869450777</v>
+        <v>0.1815804332966806</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.377285336679257</v>
+        <v>-2.38771497237741</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.007205</t>
+          <t>X ≈ -0.007215</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.674540682414758</v>
+        <v>-3.796705504218501</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.5617048465600547</v>
+        <v>-0.671049492019236</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.893581427172393</v>
+        <v>-5.013189297826848</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.450992336559644</v>
+        <v>-3.567174680554274</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-6.351618276041265</v>
+        <v>-6.473885286281543</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-7.628979487931907</v>
+        <v>-7.755458625067632</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-9.288516354810483</v>
+        <v>-9.419116352754791</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-8.180896603985687</v>
+        <v>-8.307237628120475</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-7.979429298566934</v>
+        <v>-8.105061889906409</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.729816950786464</v>
+        <v>-6.849717528341536</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.672103083502989</v>
+        <v>-6.791260791864886</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-7.425121500960657</v>
+        <v>-7.546356323720026</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-6.008105770698272</v>
+        <v>-6.124401913875602</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.65864690561358</v>
+        <v>-3.793403105754336</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.01048</t>
+          <t>X ≈ 0.01047</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.782836601012264</v>
+        <v>-3.623773173391626</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.534811360108328</v>
+        <v>-4.377816409312466</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.497015310257865</v>
+        <v>-3.344016365496074</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.080229226361034</v>
+        <v>-2.928076936193492</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.332117490143872</v>
+        <v>-3.180652203574972</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.602010795981208</v>
+        <v>-1.45470674536832</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.03245319448296158</v>
+        <v>0.1748686096512273</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.4248686495696532</v>
+        <v>0.5649428230073426</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.22346761725548</v>
+        <v>1.361103523627357</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.059322324219366</v>
+        <v>-0.9173867012738697</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.4044767946687529</v>
+        <v>-0.2649450023911939</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.08356068603386291</v>
+        <v>0.05514743567847091</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.363414150847021</v>
+        <v>-1.222146274777856</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.5406269159919361</v>
+        <v>-0.4249820531227471</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.02817</t>
+          <t>X ≈ 0.02816</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>319</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.992455096717961</v>
+        <v>3.004977386393584</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.634799979051472</v>
+        <v>2.647709788627523</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.120809015401555</v>
+        <v>4.133816146819157</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.878021395657996</v>
+        <v>4.89100053805646</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.399161309112543</v>
+        <v>3.412272113487482</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.950521742125972</v>
+        <v>4.963564638420337</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.552308401029208</v>
+        <v>4.565374655329684</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.712084249896613</v>
+        <v>4.72526525919185</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.710645492241028</v>
+        <v>3.723844231195791</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.800959178686412</v>
+        <v>3.814364306339243</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.596205854368804</v>
+        <v>3.609663148079022</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.749711268767491</v>
+        <v>1.763163557487601</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.956415905471516</v>
+        <v>1.969971951823119</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.892657613923362</v>
+        <v>1.88222797822521</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.04587</t>
+          <t>X ≈ 0.04584</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>278</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3842595215166824</v>
+        <v>0.3967818111923052</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.247506052437245</v>
+        <v>5.260415862013296</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>7.010910727135617</v>
+        <v>7.023917858553219</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>7.500876089958986</v>
+        <v>7.51385523235745</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>6.602742644670975</v>
+        <v>6.615853449045915</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.101623431307466</v>
+        <v>5.114666327601832</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7.175163095330198</v>
+        <v>7.188229349630674</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>5.62884300590121</v>
+        <v>5.642024015196448</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>6.646979810366396</v>
+        <v>6.660178549321159</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>6.516279085770073</v>
+        <v>6.529684213422904</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>7.03095022188419</v>
+        <v>7.044407515594408</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>5.626484458366271</v>
+        <v>5.639936747086381</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.047956466126443</v>
+        <v>3.061512512478046</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.578253337971084</v>
+        <v>2.567823702272932</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.06356</t>
+          <t>X ≈ 0.06354</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>229</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.401735263441367</v>
+        <v>-1.389212973765744</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.139946430990769</v>
+        <v>-2.127036621414717</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.534815137587458</v>
+        <v>-2.521808006169856</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.841243227687343</v>
+        <v>-2.828264085288879</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.253026888174404</v>
+        <v>-4.239916083799464</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.449034732118086</v>
+        <v>-7.435991835823721</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-8.407130894805206</v>
+        <v>-8.39406464050473</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-6.69090818004959</v>
+        <v>-6.677727170754352</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-5.005183175402202</v>
+        <v>-4.991984436447439</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.361858578770736</v>
+        <v>-2.348453451117905</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.313336793918012</v>
+        <v>-4.299879500207794</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-4.278953636572581</v>
+        <v>-4.265501347852471</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.262527024810062</v>
+        <v>-4.248970978458459</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.012805692533775</v>
+        <v>-4.023235328231927</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.08125</t>
+          <t>X ≈ 0.08122</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.140708021253388</v>
+        <v>1.930848675347939</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4464753478083736</v>
+        <v>-0.6607295745785748</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.79256356660003</v>
+        <v>-2.526089194627616</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-8.515968970577902</v>
+        <v>-8.278216992215839</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.176341405162262</v>
+        <v>-3.914545760997754</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.464265321105195</v>
+        <v>-0.1857991823431178</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.500218550572598</v>
+        <v>-2.231293855334769</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.4472321969873718</v>
+        <v>0.7330100498980983</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.028401835536343</v>
+        <v>-2.759344655644341</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.9516977522716417</v>
+        <v>-0.6680869813859047</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.156451076589221</v>
+        <v>-0.8727881396460972</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.122067919243847</v>
+        <v>-0.8384099872907242</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.07890789604235948</v>
+        <v>0.212027394689926</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.8047963198636765</v>
+        <v>-0.5426291119462832</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.09895</t>
+          <t>X ≈ 0.09888</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.1755575255079904</v>
+        <v>0.1506629168340652</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.524127139673446</v>
+        <v>1.828950507980771</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-6.817761434472807</v>
+        <v>-7.118452455721716</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.038501679348826</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.576922894420917</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.292725989817846</v>
+        <v>-2.623879677699151</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.052956395831849</v>
+        <v>-1.392800563281099</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.182391450242484</v>
+        <v>-2.517763943909955</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.4056152860916953</v>
+        <v>0.05283284693576462</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.879993412322122</v>
+        <v>0.5187035242900393</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.6752400880045428</v>
+        <v>0.3140023660298468</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.04737158972091038</v>
+        <v>-0.3095142184570037</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.684141299369763</v>
+        <v>-4.019138755980869</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.434419967093362</v>
+        <v>-3.793403105754294</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.1167</t>
+          <t>X ≈ 0.1166</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>115</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.058655711514326</v>
+        <v>-2.046133421838704</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>5.894988066825768</v>
+        <v>5.907897876401819</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.630554142837823</v>
+        <v>4.643561274255426</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.282546405880154</v>
+        <v>1.295525548278619</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.61369040819929</v>
+        <v>1.626801212574229</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.041567128523596</v>
+        <v>1.054610024817961</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.913355150381811</v>
+        <v>7.926421404682287</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.09834566464378</v>
+        <v>3.111526673939018</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.515606648026697</v>
+        <v>6.52880538698146</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.404611897781379</v>
+        <v>7.41801702543421</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.330293356072502</v>
+        <v>6.34375064978272</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.495111296026579</v>
+        <v>5.508563584746689</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.944421902473032</v>
+        <v>5.957977948824634</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.933273669531872</v>
+        <v>7.922844033833719</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>104</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10.00656167978997</v>
+        <v>10.01908396946559</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.510372682210381</v>
+        <v>5.523282491786432</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.192427052536864</v>
+        <v>3.205434183954466</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.361141723605904</v>
+        <v>2.374120866004368</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.745797431610612</v>
+        <v>3.758908235985551</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.1970855231725253</v>
+        <v>0.2101284194668906</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.073890267438664</v>
+        <v>1.08695652173914</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.568245330195616</v>
+        <v>1.581426339490854</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.507245444013314</v>
+        <v>1.520444182968077</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.541735643600774</v>
+        <v>3.555140771253605</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>10.06775155005242</v>
+        <v>10.08120884376264</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.179057784320989</v>
+        <v>8.192510073041099</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>15.45111086568372</v>
+        <v>15.46466691203533</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>15.70083219795995</v>
+        <v>15.6904025622618</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>99</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.041915215143618</v>
+        <v>1.054437504819241</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>1.463453431957376</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.075876935986813</v>
+        <v>3.088884067404415</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.226332088796269</v>
+        <v>5.239311231194733</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.647506833320179</v>
+        <v>0.6606176376951183</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>7.005554831641781</v>
+        <v>7.018597727936147</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.920821114369559</v>
+        <v>6.933887368670035</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.443536705486999</v>
+        <v>5.456717714782236</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.382536819304697</v>
+        <v>5.39573555825946</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.55261365447879</v>
+        <v>6.566018782131621</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.327658309959247</v>
+        <v>4.341115603669465</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.402445507708663</v>
+        <v>8.415897796428773</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.982190896763761</v>
+        <v>7.995746943115364</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>10.25211424924218</v>
+        <v>10.24168461354403</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>66</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>8.112622285850634</v>
+        <v>8.125144575526257</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>15.59195776379547</v>
+        <v>15.60486757337152</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>19.74254360265343</v>
+        <v>19.75555073407103</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>9.266736129200311</v>
+        <v>9.279715271598775</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>10.24346642927956</v>
+        <v>10.2565772336545</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>10.54090836699532</v>
+        <v>10.55395126328969</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>11.97132616487448</v>
+        <v>11.98439241917495</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.988991250941488</v>
+        <v>10.00217226023673</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>12.95829439506226</v>
+        <v>12.97149313401702</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>12.10816921003433</v>
+        <v>12.12157433768716</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>10.38826437056517</v>
+        <v>10.40172166427539</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>13.45295055821367</v>
+        <v>13.46640284693378</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.51754443211728</v>
+        <v>11.53110047846889</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>13.28241727954502</v>
+        <v>13.27198764384686</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>66</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.567167740396044</v>
+        <v>3.579690030071667</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.985897157734861</v>
+        <v>4.998806967310912</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>9.136482996592811</v>
+        <v>9.149490128010413</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8.728314914128141</v>
+        <v>8.741425718503081</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>9.025756851843802</v>
+        <v>9.038799748138167</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>11.98439241917502</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>14.53444579639612</v>
+        <v>14.54762680569136</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.927991364759244</v>
+        <v>9.941190103714007</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>12.10816921003433</v>
+        <v>12.12157433768716</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>14.96810207336527</v>
+        <v>14.98155436208538</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.51754443211728</v>
+        <v>11.53110047846889</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>7.221811218939031</v>
+        <v>7.211381583240879</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>69</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>8.376126897181365</v>
+        <v>8.388649186856988</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>9.663104008854745</v>
+        <v>9.676013818430796</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.818959939939369</v>
+        <v>7.831967071356971</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>17.5557193937065</v>
+        <v>17.56883019808144</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>14.95461060678456</v>
+        <v>14.96765350307892</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14.86987688951223</v>
+        <v>14.88294314381271</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>23.09834566464374</v>
+        <v>23.11152667393898</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>21.58807041614261</v>
+        <v>21.60126915509737</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>19.28866986879588</v>
+        <v>19.30207499644871</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.87192289022953</v>
+        <v>11.88537517894964</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12.9009436416035</v>
+        <v>12.9144996879551</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>44</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.597470770699118</v>
+        <v>6.609993060374741</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>11.80407897591667</v>
+        <v>11.81698878549273</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>18.22739208750184</v>
+        <v>18.24039921891944</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>20.63037249283668</v>
+        <v>20.64335163523514</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>17.81922400503727</v>
+        <v>17.83233480941221</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>22.66212048820738</v>
+        <v>22.67516338450174</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>18.03193222548065</v>
+        <v>18.04499847978113</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>15.29202155397194</v>
+        <v>15.30520256326718</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>17.50374894051685</v>
+        <v>17.51694767947161</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.835441937307067</v>
+        <v>9.848847064959898</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>20.99432497662585</v>
+        <v>21.00778227033607</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>23.30143540669856</v>
+        <v>23.31488769541867</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>27.4266353412081</v>
+        <v>27.44019138755971</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>20.85817485530264</v>
+        <v>20.84774521960448</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>42</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.023928884038732</v>
+        <v>5.036936015456334</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.154182016646203</v>
+        <v>5.167161159044667</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.615760801574062</v>
+        <v>4.628871605949001</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>7.294155120242074</v>
+        <v>7.307198016536439</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16.73323092677932</v>
+        <v>16.7462971810798</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>16.26604752799782</v>
+        <v>16.27922853729306</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.45634161886551</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>15.35492245678759</v>
+        <v>15.36832758444042</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.76921675151763</v>
+        <v>12.78267404522785</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>15.18455228981547</v>
+        <v>15.19800457853558</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>17.14525005982296</v>
+        <v>17.15880610617457</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>19.77592377305162</v>
+        <v>19.76549413735346</v>
       </c>
     </row>
     <row r="32">
@@ -1927,150 +1927,150 @@
         <v>23</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-13.36300353760134</v>
+        <v>-13.35048124792571</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.931098889695974</v>
+        <v>-1.918189080119923</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.021858490663902</v>
+        <v>2.034865622081504</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.499937710227989</v>
+        <v>6.512916852626454</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>10.30934258211234</v>
+        <v>10.32245338648728</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>10.606784519828</v>
+        <v>10.61982741612236</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-2.521427458313909</v>
+        <v>-2.508361204013433</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.988610857095409</v>
+        <v>-2.975429847800172</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.049610743277583</v>
+        <v>-3.03641200432282</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.795916245607401</v>
+        <v>4.809321373260232</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-4.104489252623218</v>
+        <v>-4.091031958913</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-8.41793218223431</v>
+        <v>-8.4044798935142</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1425346192661081</v>
+        <v>-0.1289785729145052</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.802838886923226</v>
+        <v>8.792409251225074</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.2759</t>
+          <t>X ≈ 0.2758</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>23</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>12.72395298413791</v>
+        <v>12.73647527381353</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-6.27892497665249</v>
+        <v>-6.266015167076439</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-15.36944585716213</v>
+        <v>-15.35643872574452</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-6.54354055064158</v>
+        <v>-6.530561408243116</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-7.081961765713785</v>
+        <v>-7.068850961338846</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-15.48017200191114</v>
+        <v>-15.46712910561677</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-11.21707963222689</v>
+        <v>-11.20401337792642</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-11.68426303100839</v>
+        <v>-11.67108202171315</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-11.74526291719069</v>
+        <v>-11.73206417823593</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-12.59538810221856</v>
+        <v>-12.58198297456573</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-12.80014142653614</v>
+        <v>-12.78668413282593</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-8.417932182234246</v>
+        <v>-8.404479893514136</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1425346192661081</v>
+        <v>-0.1289785729145052</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.240639373946344</v>
+        <v>-4.251069009644496</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.2935</t>
+          <t>X ≈ 0.2934</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>12.16678602689581</v>
+        <v>12.17979315831341</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>17.85259471505889</v>
+        <v>17.86557385745736</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>17.31417349998681</v>
+        <v>17.32728430436175</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>17.61161543770238</v>
+        <v>17.62465833399675</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.415770609319004</v>
+        <v>6.42883686361948</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.948587210537504</v>
+        <v>5.961768219832742</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.45634161886551</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.59301769488279</v>
+        <v>10.60642282253562</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.832708815009696</v>
+        <v>4.846166108719913</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.867091972355126</v>
+        <v>4.880544261075237</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.108718194145375</v>
+        <v>-1.095162147793772</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.8589968618690449</v>
+        <v>-0.869426497567197</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-30 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-30 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.09029952668373653</v>
+        <v>-0.09062429236323055</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.101512472025675</v>
+        <v>0.1011298528608648</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.01434899712810278</v>
+        <v>0.01398496601518673</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.01379928630442606</v>
+        <v>-0.01415572492187067</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.05022324634575881</v>
+        <v>0.0498473582130643</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1647430804445662</v>
+        <v>0.1643408736793006</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1916928970291067</v>
+        <v>0.191283326777949</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.27839970542</v>
+        <v>0.2779655566587564</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.4275818643497331</v>
+        <v>0.4271104717272181</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.3284154175009917</v>
+        <v>0.3279625440753762</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.3096016370352572</v>
+        <v>0.3091518272966809</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1857816972410546</v>
+        <v>0.1853623535039475</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.295883653152039</v>
+        <v>0.2954342514085226</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2644143722432943</v>
+        <v>0.2646391962623937</v>
       </c>
     </row>
     <row r="7">
@@ -2269,150 +2269,150 @@
         <v>4045</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.05381288896305847</v>
+        <v>-0.06593328041113722</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.02365456916739817</v>
+        <v>0.01191562350559394</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.03735598493847903</v>
+        <v>-0.04900368586801562</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.04163737152830294</v>
+        <v>-0.05331914158359297</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.02398360136722033</v>
+        <v>-0.03553979255222117</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1142883548830724</v>
+        <v>0.102658169509553</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.141776971060807</v>
+        <v>0.1301640545814209</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.2558913055483316</v>
+        <v>0.244387051945516</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.3814144848490315</v>
+        <v>0.3699218657790979</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2612485337730845</v>
+        <v>0.2499562052638993</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2680403916456129</v>
+        <v>0.2567941280435804</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1928476761686468</v>
+        <v>0.1815903034111201</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2808572438730081</v>
+        <v>0.2696975215642041</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1985501783726775</v>
+        <v>0.1881205426745254</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.1753</t>
+          <t>X &gt; -0.1752</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4008</v>
+        <v>4009</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.01892949156038526</v>
+        <v>-0.01945407131008636</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.09896816632825534</v>
+        <v>0.09839775205463752</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.05847730560809339</v>
+        <v>-0.05901281183580664</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.01422681029921335</v>
+        <v>-0.01477227618561727</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01633849071943416</v>
+        <v>-0.01688913737274333</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.09556851428494895</v>
+        <v>0.09499274607874497</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.14899324665123</v>
+        <v>0.148403043345013</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2435548238907614</v>
+        <v>0.2429360626444179</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3458756650257939</v>
+        <v>0.3452305077544082</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2822832316059944</v>
+        <v>0.2816450170700833</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.266100321699632</v>
+        <v>0.265463771287763</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2647090407951396</v>
+        <v>0.2640728906771628</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2825957938261752</v>
+        <v>0.2819506258277755</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.2221741294815871</v>
+        <v>0.2225609750638213</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.1576</t>
+          <t>X &gt; -0.1575</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3973</v>
+        <v>3974</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1100966242742061</v>
+        <v>-0.1107128702634768</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.04806209442927667</v>
+        <v>0.04738608513237352</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1324107602527533</v>
+        <v>-0.1330466576631295</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1140412656368355</v>
+        <v>-0.114680493278918</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1114640913967193</v>
+        <v>-0.1121109030476006</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.02390715670096455</v>
+        <v>0.02322968284434523</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1539057293636716</v>
+        <v>0.1531942277658445</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2785416937968321</v>
+        <v>0.277792787113583</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.357170029232023</v>
+        <v>0.3564002600651435</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.250213235910401</v>
+        <v>0.2494595243958884</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1853804000756512</v>
+        <v>0.1846401120166377</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.0830248864012475</v>
+        <v>0.08231041354560631</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1047247404853167</v>
+        <v>0.1039992777827905</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.06669600945684806</v>
+        <v>0.06721724229747394</v>
       </c>
     </row>
     <row r="10">
@@ -2425,46 +2425,46 @@
         <v>3911</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1355489498301665</v>
+        <v>-0.1363696492907209</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1275224880394319</v>
+        <v>0.1266080471894853</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1515001245961258</v>
+        <v>-0.1523503059054931</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1094234255306645</v>
+        <v>-0.1102826417350116</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.09814823741793788</v>
+        <v>-0.09901955051361</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.06014359832855831</v>
+        <v>0.05923631590823675</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.09148615125869242</v>
+        <v>0.09056903989988996</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.200091012603103</v>
+        <v>0.1991380890637231</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2043178479822743</v>
+        <v>0.2033623883581939</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1348333991921464</v>
+        <v>0.1338813155113954</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1233355009852204</v>
+        <v>0.1223825397651623</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.04432441952621957</v>
+        <v>0.04339174950411717</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.02199574659162096</v>
+        <v>0.02106143775500868</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.01602799679171341</v>
+        <v>0.005598361093561266</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3843</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2236588130763764</v>
+        <v>-0.2246919641443057</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.005375192125967487</v>
+        <v>-0.00649901075771453</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.230480172602384</v>
+        <v>-0.2315543594170535</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1640200305278157</v>
+        <v>-0.1651093042924998</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1690198985533371</v>
+        <v>-0.1701196416404116</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.03874386483081338</v>
+        <v>0.03759581055406613</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.005810753805626234</v>
+        <v>-0.006949572166959683</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1649189268692197</v>
+        <v>0.1637254381578472</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1962838555627755</v>
+        <v>0.1950803576042546</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1145985581173505</v>
+        <v>0.1133979546732533</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2105443879037878</v>
+        <v>0.209313967967617</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1295500599953172</v>
+        <v>0.1283408222658196</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.06224199320829626</v>
+        <v>0.06104088145820441</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.0002927244763810677</v>
+        <v>-0.01072236017453321</v>
       </c>
     </row>
     <row r="12">
@@ -2529,98 +2529,98 @@
         <v>3743</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1619701614036799</v>
+        <v>-0.1633880603691935</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1604490333874438</v>
+        <v>-0.1619129416104386</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4076385709891639</v>
+        <v>-0.4090483484385032</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4496275071633207</v>
+        <v>-0.4510231981426287</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5202119657671034</v>
+        <v>-0.5216045845272248</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2349397621078779</v>
+        <v>-0.2364009114316588</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1183455725153522</v>
+        <v>-0.1198409497328257</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.01036159411338389</v>
+        <v>-0.01189960331466722</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.003230061789295746</v>
+        <v>-0.0047724583724289</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1496416265067566</v>
+        <v>0.1480338594737916</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.173641519020137</v>
+        <v>0.1720208095746116</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1813081388288396</v>
+        <v>0.1947604275489496</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.1350850533982282</v>
+        <v>0.1486410997498311</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.0159416773765102</v>
+        <v>-0.02637131307466234</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.08681</t>
+          <t>X &gt; -0.0868</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3621</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.124292314700341</v>
+        <v>-0.1261928137896504</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.04213604147443561</v>
+        <v>0.04012928136049254</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2551176849747918</v>
+        <v>-0.2570581322165424</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2477637078801678</v>
+        <v>-0.2497023890206478</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5230514800953898</v>
+        <v>-0.524935160761018</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2657791983129272</v>
+        <v>-0.2677238440997129</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1699541883263223</v>
+        <v>-0.1719294199054247</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1804648335021213</v>
+        <v>-0.1824554740598288</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1434575250220647</v>
+        <v>-0.1454616749057607</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.07106243390519751</v>
+        <v>0.06896653687395826</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1424759143376875</v>
+        <v>0.1559332080479052</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1492423912081122</v>
+        <v>0.1626946799282223</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1708546678633169</v>
+        <v>0.1844107142149198</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.08917583443952282</v>
+        <v>0.07874619874137068</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>3472</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.194587745497337</v>
+        <v>-0.1970895438925808</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.06649511799745511</v>
+        <v>-0.06911361785105186</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3883222728932978</v>
+        <v>-0.3908689093305142</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3000272770799199</v>
+        <v>-0.302594310710802</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.7941246716025816</v>
+        <v>-0.7965772621228453</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1802270376843893</v>
+        <v>-0.1671841413900239</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.1341894226554174</v>
+        <v>-0.1368197020370943</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.06753253615219279</v>
+        <v>-0.07020620063089211</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.08888623339957746</v>
+        <v>0.08616315024145393</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3203602448060181</v>
+        <v>0.3175275350800533</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2020124504423677</v>
+        <v>0.2154697441525855</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2939992944237417</v>
+        <v>0.3074515831438518</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.3633760198843632</v>
+        <v>0.3769320662359661</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.2674752323449852</v>
+        <v>0.257045596646833</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>3271</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.01267414922767074</v>
+        <v>0.02519643890329348</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.5571708855356405</v>
+        <v>0.553374649017961</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1317304883245569</v>
+        <v>0.144737619742159</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1396968584741032</v>
+        <v>0.1526760008725674</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2152942129111182</v>
+        <v>-0.2021834085361789</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3878646309494442</v>
+        <v>0.4009075272438096</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5477044385930867</v>
+        <v>0.5607706928935627</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.7225265427159115</v>
+        <v>0.7357075520111493</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7838134189915635</v>
+        <v>0.7970121579463267</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.125984167928785</v>
+        <v>1.139389295581616</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.9823742248401857</v>
+        <v>0.9958315185504034</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.047329072800117</v>
+        <v>1.060781361520228</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.116221511687066</v>
+        <v>1.129777558038668</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.182512700276405</v>
+        <v>1.172083064578253</v>
       </c>
     </row>
     <row r="16">
@@ -2737,566 +2737,566 @@
         <v>2987</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1011381779487124</v>
+        <v>0.1136604676243351</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.7995746085063757</v>
+        <v>0.8124844180824269</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.5386195276212149</v>
+        <v>0.551626659038817</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.6353942538008539</v>
+        <v>0.6483733961993181</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.163929851584399</v>
+        <v>0.1770406559593383</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3944149764443452</v>
+        <v>0.4074578727387106</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.8453357620177329</v>
+        <v>0.8584020163182089</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.248590930360443</v>
+        <v>1.261771939655681</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.321504669889549</v>
+        <v>1.334703408844312</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.576166896980801</v>
+        <v>1.589572024633632</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.505327198374644</v>
+        <v>1.518784492084862</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.372318323580807</v>
+        <v>1.385770612300917</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.420761402625857</v>
+        <v>1.43431744897746</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.436133889907168</v>
+        <v>1.425704254209016</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.01605</t>
+          <t>X &gt; -0.01606</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2665</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3771057698463096</v>
+        <v>0.3896280595219324</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.354650355756348</v>
+        <v>1.367560165332399</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.8847347448445646</v>
+        <v>0.8977418762621667</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.127558233924859</v>
+        <v>1.140537376323323</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2514259494343065</v>
+        <v>0.2645367538092458</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.4738209828347593</v>
+        <v>0.4868638791291247</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.9894625000840591</v>
+        <v>1.002528754384535</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.272748144454532</v>
+        <v>1.28592915374977</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.474412423375419</v>
+        <v>1.487611162330182</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.900084611705843</v>
+        <v>1.913489739358674</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.770378191703458</v>
+        <v>1.783835485413675</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.579620636103307</v>
+        <v>1.593072924823417</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.572123998891982</v>
+        <v>1.585680045243585</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.896892235483463</v>
+        <v>1.886462599785311</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.001639</t>
+          <t>X &gt; 0.00163</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.052971487145548</v>
+        <v>1.085823575592556</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.674322567701424</v>
+        <v>1.706584966117354</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.848630743766833</v>
+        <v>1.880741371296665</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.89131820211864</v>
+        <v>1.923439162587435</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.352896987046471</v>
+        <v>1.385149609491741</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.82547027327351</v>
+        <v>1.857578343722018</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.703958972813851</v>
+        <v>2.735668859729373</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.849735293822185</v>
+        <v>2.88129168202579</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.051432430406962</v>
+        <v>3.082891582395781</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.339661010703026</v>
+        <v>3.370828365934642</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.178690523513289</v>
+        <v>3.209890883823235</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.081725169475192</v>
+        <v>3.112978007732174</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.836601907041668</v>
+        <v>2.867881859013956</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.823626216550878</v>
+        <v>2.831035452347706</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.01933</t>
+          <t>X &gt; 0.01932</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1935</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.92516633095282</v>
+        <v>1.937688620628442</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.79421287302732</v>
+        <v>2.807122682603371</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.812780858937181</v>
+        <v>2.825787990354783</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.787995231854765</v>
+        <v>2.800974374253229</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.197894430219293</v>
+        <v>2.211005234594232</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.443656781371644</v>
+        <v>2.456699677666009</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.185796449112281</v>
+        <v>3.198862703412757</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.287088502527162</v>
+        <v>3.3002695118224</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.38112737603479</v>
+        <v>3.394326114989553</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.133069374469393</v>
+        <v>4.146474502122224</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.824956877025194</v>
+        <v>3.838414170735412</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.652621688117392</v>
+        <v>3.666073976837502</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.594124183115646</v>
+        <v>3.607680229467249</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.430408822885475</v>
+        <v>3.419979187187323</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.03702</t>
+          <t>X &gt; 0.037</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1616</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.714482471869239</v>
+        <v>1.727004761544862</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.825681136132694</v>
+        <v>2.838590945708745</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.554574805773726</v>
+        <v>2.567581937191328</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.375421997787171</v>
+        <v>2.388401140185636</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.960763158952631</v>
+        <v>1.97387396332757</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.948799156074223</v>
+        <v>1.961842052368588</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.91604563682175</v>
+        <v>2.929111891122226</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.005792931109553</v>
+        <v>3.018973940404791</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.316080173640124</v>
+        <v>3.329278912594887</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.198628255938928</v>
+        <v>4.212033383591759</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.870112555383727</v>
+        <v>3.883569849093945</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.02825808896678</v>
+        <v>4.04171037768689</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.917409418615946</v>
+        <v>3.930965464967549</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.733962434060544</v>
+        <v>3.723532798362392</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.05471</t>
+          <t>X &gt; 0.05469</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1338</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.990866612525451</v>
+        <v>2.003388902201074</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.322491803746551</v>
+        <v>2.335401613322603</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.628669434967591</v>
+        <v>1.641676566385193</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.31049207430155</v>
+        <v>1.323471216700014</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.9962861058661474</v>
+        <v>1.009396910241087</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.293728043581808</v>
+        <v>1.306770939876174</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.03111689731103</v>
+        <v>2.044183151611506</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.460794485076612</v>
+        <v>2.473975494371849</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.624009845531084</v>
+        <v>2.637208584485847</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.717083464688507</v>
+        <v>3.730488592341338</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.213376478188565</v>
+        <v>3.226833771898782</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.696190128807537</v>
+        <v>3.709642417527647</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.098058088864128</v>
+        <v>4.111614135215731</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.974087343412471</v>
+        <v>3.963657707714319</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0724</t>
+          <t>X &gt; 0.07238</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1109</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.691412897102914</v>
+        <v>2.703935186778537</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.243951096582308</v>
+        <v>3.256860906158359</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.488397087911778</v>
+        <v>2.50140421932938</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.167793592926849</v>
+        <v>2.180772735325313</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.080229005447109</v>
+        <v>2.093339809822048</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.099041547310648</v>
+        <v>3.112084443605013</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.186535061778677</v>
+        <v>4.199601316079153</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4.350550941626565</v>
+        <v>4.363731950921803</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.199379729925781</v>
+        <v>4.212578468880544</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.972338404230591</v>
+        <v>4.985743531883422</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.767585079913012</v>
+        <v>4.781042373623229</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>5.342996190369348</v>
+        <v>5.356448479089458</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5.824454834609305</v>
+        <v>5.838010880960908</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5.623319539293156</v>
+        <v>5.612889903595004</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.09009</t>
+          <t>X &gt; 0.09006</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.81629619306436</v>
+        <v>2.878199991565097</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.080828774790369</v>
+        <v>4.139942075296844</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.685960068193779</v>
+        <v>3.634673452972741</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.590549483987111</v>
+        <v>4.538379259544534</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.499030923782207</v>
+        <v>3.447603518603536</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.907092330524421</v>
+        <v>3.855474785807687</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.702889586703463</v>
+        <v>5.64921746521555</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.235706187921963</v>
+        <v>5.182148821428811</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.838423115898948</v>
+        <v>5.784150090320402</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>6.315731559189608</v>
+        <v>6.26019814481927</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>6.110978234872029</v>
+        <v>6.055496986559078</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.809078206376761</v>
+        <v>6.752858564328754</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7.163159878617698</v>
+        <v>7.106188373998776</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>7.081022803814342</v>
+        <v>7.000432311518132</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.1078</t>
+          <t>X &gt; 0.1077</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>753</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.416256234902903</v>
+        <v>3.428778524578526</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.593527243452598</v>
+        <v>4.60643705302865</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.792284034863975</v>
+        <v>5.805291166281577</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.320943541973463</v>
+        <v>6.333922684371927</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.118511702731311</v>
+        <v>5.13162250710625</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.150349390778977</v>
+        <v>5.163392287073343</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.057647546016653</v>
+        <v>7.070713800317129</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.723266272069154</v>
+        <v>6.736447281364391</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.927870635554847</v>
+        <v>6.94106937450961</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.405766698866891</v>
+        <v>7.419171826519722</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>7.201013374549312</v>
+        <v>7.21447066825953</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>8.165011405732727</v>
+        <v>8.178463694452837</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>9.338382292795792</v>
+        <v>9.351938339147395</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>9.189697250570077</v>
+        <v>9.179267614871925</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.1255</t>
+          <t>X &gt; 0.1254</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>638</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.403113403927961</v>
+        <v>4.415635693603583</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.358937910085956</v>
+        <v>4.371847719662007</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.001686758348306</v>
+        <v>6.014693889765908</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7.229118574341385</v>
+        <v>7.242097716739849</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>5.750258487795854</v>
+        <v>5.763369292170793</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>5.890960613599297</v>
+        <v>5.904003509893663</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.903405579712597</v>
+        <v>6.916471834013073</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.376661052404444</v>
+        <v>7.389842061699682</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.002181542397693</v>
+        <v>7.015380281352456</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.405974852667576</v>
+        <v>7.419379980320407</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.357961340262214</v>
+        <v>7.371418633972432</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.646262992905463</v>
+        <v>8.659715281625573</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>9.950146312995038</v>
+        <v>9.963702359346641</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>9.416168585710196</v>
+        <v>9.405738950012044</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.1432</t>
+          <t>X &gt; 0.1431</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>534</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.311805125482913</v>
+        <v>3.324327415158535</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.134688441357603</v>
+        <v>4.147598250933655</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.548808498805961</v>
+        <v>6.561815630223563</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>8.177188972237424</v>
+        <v>8.190168114635888</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.140640416341292</v>
+        <v>6.153751220716231</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.99988010686593</v>
+        <v>7.012923003160296</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.038741895211636</v>
+        <v>8.051808149512112</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.507888084445113</v>
+        <v>8.521069093740351</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8.072356363056819</v>
+        <v>8.085555102011583</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.158560766043877</v>
+        <v>8.171965893696708</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.83021193610832</v>
+        <v>6.843669229818538</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.737254269483714</v>
+        <v>8.750706558203824</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>8.878797411347797</v>
+        <v>8.8923534576994</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.192189155609114</v>
+        <v>8.181759519910962</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>435</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.828400760249792</v>
+        <v>3.840923049925415</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.745562779469445</v>
+        <v>4.758472589045496</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>7.339199819999294</v>
+        <v>7.352206951416896</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.848763297434381</v>
+        <v>8.861742439832845</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.390801852477146</v>
+        <v>7.403912656852086</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.998588617779021</v>
+        <v>7.011631514073386</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.293165245334322</v>
+        <v>8.306231499634798</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.205292191380416</v>
+        <v>9.218473200675653</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.684522190255585</v>
+        <v>8.697720929210348</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>8.524052177641451</v>
+        <v>8.537457305294282</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.399758623438807</v>
+        <v>7.413215917149024</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>8.813452125611832</v>
+        <v>8.826904414331942</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.082852687080724</v>
+        <v>9.096408733432327</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.723378617058145</v>
+        <v>7.712948981359993</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>369</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.074639525021205</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.805557172516821</v>
+        <v>2.818466982092872</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.120715566191237</v>
+        <v>5.133722697608839</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.774003929151043</v>
+        <v>8.786983071549507</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.88056916394337</v>
+        <v>6.89367996831831</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.365002971577731</v>
+        <v>6.378045867872096</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7.635282804440948</v>
+        <v>7.648349058741424</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>9.06511837584916</v>
+        <v>9.078299385144398</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.920107649558453</v>
+        <v>7.933306388513216</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.882990594611826</v>
+        <v>7.896395722264657</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.865229140212946</v>
+        <v>6.878686433923164</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.983623137666783</v>
+        <v>7.997075426386893</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.647379366830272</v>
+        <v>8.660935413181875</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.729079018889763</v>
+        <v>6.718649383191611</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>303</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.952106234245477</v>
+        <v>2.9646285239211</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.3306316311822</v>
+        <v>2.343541440758251</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.245993947687921</v>
+        <v>4.259001079105524</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.006610116599056</v>
+        <v>8.01958925899752</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.478089891625892</v>
+        <v>6.491200696000831</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.785432819440565</v>
+        <v>5.798475715734931</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.690798112069274</v>
+        <v>6.70386436636975</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.873779729789426</v>
+        <v>7.886960739084664</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.482746840306795</v>
+        <v>7.495945579261559</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6.962654658579197</v>
+        <v>6.976059786232028</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.09783532766096</v>
+        <v>6.111292621371177</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.46225148830672</v>
+        <v>6.47570377702683</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.022194897163793</v>
+        <v>8.035750943515396</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.621751212938435</v>
+        <v>6.611321577240282</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>234</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.365237815619494</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1684923403300402</v>
+        <v>0.1814021499060914</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.192427052536864</v>
+        <v>3.205434183954466</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.741483603947792</v>
+        <v>6.754462746346256</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.211609397422635</v>
+        <v>3.224720201797574</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.081700907787855</v>
+        <v>3.094743804082221</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.279018472566868</v>
+        <v>4.292084726867344</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.384484646434942</v>
+        <v>3.397665655730179</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.32348476025264</v>
+        <v>3.336683499207403</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.328060429925564</v>
+        <v>3.341465557578395</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.832708815009696</v>
+        <v>4.846166108719913</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.867091972355126</v>
+        <v>4.880544261075237</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.583589498162354</v>
+        <v>6.597145544513957</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.551259548387364</v>
+        <v>5.540829912689212</v>
       </c>
     </row>
     <row r="31">
@@ -3517,254 +3517,254 @@
         <v>190</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1381406271584424</v>
+        <v>0.1506629168340652</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.526064564753177</v>
+        <v>-2.513154755177126</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2893543239813496</v>
+        <v>-0.2763471925637475</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.525109334941945</v>
+        <v>3.538088477340409</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1712066169723272</v>
+        <v>-0.1580958125973879</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.452712047677728</v>
+        <v>-1.439669151383363</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.09413318241841</v>
+        <v>1.107199436718886</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.6269497836369098</v>
+        <v>0.6401307929321476</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.03963410798093747</v>
+        <v>0.05283284693570067</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.821087870321428</v>
+        <v>1.834492997974259</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.090018756530164</v>
+        <v>1.103476050240381</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.5980861244019025</v>
+        <v>0.6115384131220125</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.756778881878063</v>
+        <v>1.770334928229666</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.00650021415435</v>
+        <v>1.996070578456198</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.2493</t>
+          <t>X &gt; 0.2492</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>148</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.8849400581684037</v>
+        <v>0.8974623478440265</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.797177937068128</v>
+        <v>-1.784170805650525</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.062804925269113</v>
+        <v>3.075784067667577</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.529670343857113</v>
+        <v>-1.516559539482174</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-3.934931108844154</v>
+        <v>-3.921888212549788</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.343989150440763</v>
+        <v>-3.330922896140287</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.811172549222263</v>
+        <v>-3.797991539927025</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.19649675972888</v>
+        <v>-3.183298020774117</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.019594917729783</v>
+        <v>-2.006189790076952</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.224348242047363</v>
+        <v>-2.210890948337145</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-3.541316436053293</v>
+        <v>-3.527864147333183</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.610219695646833</v>
+        <v>-2.59666364929523</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.036174039046223</v>
+        <v>-3.046603674744375</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.267</t>
+          <t>X &gt; 0.2669</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.506561679790032</v>
+        <v>3.519083969465655</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.505011933174231</v>
+        <v>-4.49210212359818</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.499880639770822</v>
+        <v>-2.48687350835322</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.430372492836675</v>
+        <v>2.443351635235139</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.708048722235489</v>
+        <v>-3.69493791786055</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-6.610606784519831</v>
+        <v>-6.597563888225466</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-3.495340501792107</v>
+        <v>-3.482274247491631</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-3.962523900573608</v>
+        <v>-3.94934289127837</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.223523786755912</v>
+        <v>-3.210325047801149</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.273648971783835</v>
+        <v>-3.260243844131004</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.878402296101413</v>
+        <v>-1.864945002391195</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-2.644019138755986</v>
+        <v>-2.630566850035876</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.064273749700888</v>
+        <v>-3.050717703349285</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-5.214552417424599</v>
+        <v>-5.224982053122751</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.2847</t>
+          <t>X &gt; 0.2846</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>102</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.428130307241005</v>
+        <v>1.440652596916628</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4020801445429072</v>
+        <v>0.4150872759605093</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.453901904601388</v>
+        <v>4.466881046999852</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.947264408509994</v>
+        <v>-2.934153604135055</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.754164031203871</v>
+        <v>-1.741097776903395</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-2.221347429985371</v>
+        <v>-2.208166420690134</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.301955159304931</v>
+        <v>-1.288756420350168</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.17168818747011</v>
+        <v>-1.158283059817279</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.5843428019377939</v>
+        <v>0.5978000956480116</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.342058354442258</v>
+        <v>-1.328606065722148</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-3.72309727911265</v>
+        <v>-3.709541232761048</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-5.43416026056186</v>
+        <v>-5.444589896260013</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.3024</t>
+          <t>X &gt; 0.3023</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.280988731370414</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-2.118928258818435</v>
+        <v>-2.105921127400833</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.582753445217634</v>
+        <v>1.595732587616098</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.289001103187879</v>
+        <v>-7.275890298812939</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-9.37251154642459</v>
+        <v>-9.359468650130225</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-3.50486431131592</v>
+        <v>-3.491798057015444</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-3.972047710097421</v>
+        <v>-3.958866700802183</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-4.033047596279722</v>
+        <v>-4.019848857324959</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-3.692696590831453</v>
+        <v>-3.679291463178622</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3260213437204627</v>
+        <v>-0.3125640500102449</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-2.672590567327418</v>
+        <v>-2.659138278607308</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-4.283321368748503</v>
+        <v>-4.2697653223969</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-30 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-30 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.83989501312336</v>
+        <v>5.852417302798983</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.724059552221846</v>
+        <v>-1.711149742645794</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2620241221339441</v>
+        <v>0.2750312535515462</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1461439603307255</v>
+        <v>-0.1330331559557862</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.420130594043641</v>
+        <v>-3.407087697749276</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.314388120839723</v>
+        <v>-2.301321866539247</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-6.3530000910498</v>
+        <v>-6.339819081754563</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-11.17590473913687</v>
+        <v>-11.16270600018211</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-7.264125162260029</v>
+        <v>-7.250720034607198</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.468878486577609</v>
+        <v>-7.455421192867391</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2916381863750317</v>
+        <v>-0.2781858976549216</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-5.4737975592247</v>
+        <v>-5.460241512873097</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.033600036472215</v>
+        <v>-4.044029672170367</v>
       </c>
     </row>
     <row r="7">
@@ -3960,153 +3960,153 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.275792449020798</v>
+        <v>3.709560159941837</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.664218836056541</v>
+        <v>2.098374066878009</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.230888590998404</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.322680185144364</v>
+        <v>3.738589730473244</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.784258970072194</v>
+        <v>3.200300177377549</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.7644529383659844</v>
+        <v>-0.311849602511181</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1123518059002038</v>
+        <v>0.5558209906036069</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-4.200985439035151</v>
+        <v>-3.720771462706949</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-7.146600709832832</v>
+        <v>-6.63889647637258</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.189033587168453</v>
+        <v>-2.726910510797673</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.355325373024492</v>
+        <v>-3.883992621438814</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.4747883695252142</v>
+        <v>-0.04009065955968794</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-3.779658365085503</v>
+        <v>-3.317384370015951</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.6453216481938284</v>
+        <v>-0.2345058626465644</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.1753</t>
+          <t>X &lt; -0.1752</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>141</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.407270899648182</v>
+        <v>1.419793189323805</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.9135225714721074</v>
+        <v>-0.9006127618960562</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.237708012711451</v>
+        <v>2.250715144129053</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.658741287162918</v>
+        <v>1.671720429561383</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.829539930246781</v>
+        <v>1.842650734621721</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.0006777065056482456</v>
+        <v>0.01236518978871715</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.0854114237779271</v>
+        <v>-0.07234516947745107</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.680254397027511</v>
+        <v>-2.667073387732273</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.15969399952187</v>
+        <v>-4.146495260567107</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.882159610081715</v>
+        <v>-2.868754482428884</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.086912934399294</v>
+        <v>-3.073455640689076</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.34330991889783</v>
+        <v>-2.32985763017772</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.763564529842732</v>
+        <v>-2.750008483491129</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.095403481254387</v>
+        <v>-1.105833116952539</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.1576</t>
+          <t>X &lt; -0.1575</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>176</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.188379861608205</v>
+        <v>3.200902151283827</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>0.4533524218563585</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.454664814774638</v>
+        <v>3.46767194619224</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.584917947382138</v>
+        <v>3.597897089780602</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.614678550491782</v>
+        <v>3.627789354866721</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.639393215480169</v>
+        <v>1.652436111774534</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-0.1368197020370943</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.889796627846337</v>
+        <v>-2.876615618551099</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.518978332210452</v>
+        <v>-3.505779593255689</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.5281944263293</v>
+        <v>-1.514789298676469</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5965841142832389</v>
+        <v>-0.5831268205730211</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.278708133971286</v>
+        <v>2.292160422691396</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.858453523026384</v>
+        <v>1.872009569377987</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.676356673484491</v>
+        <v>2.665927037786339</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.736687202802578</v>
+        <v>2.749209492478201</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.9669366193666988</v>
+        <v>-0.9540268097906477</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.822295092446751</v>
+        <v>2.835302223864353</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.534138183213251</v>
+        <v>2.547117325611715</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.414127009982082</v>
+        <v>2.427237814357021</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.6195187384927223</v>
+        <v>0.6325616347870877</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.9531950630614432</v>
+        <v>0.9662613173619192</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.7692184612430708</v>
+        <v>-0.756037451947833</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.006601736256641288</v>
+        <v>0.01980047521140449</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.8301167185927341</v>
+        <v>0.8435218462455651</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.6253633942751549</v>
+        <v>0.6388206879853726</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.333386718984599</v>
+        <v>2.346839007704709</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.749952191721704</v>
+        <v>2.763508238073307</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.829145061566997</v>
+        <v>2.989243888299839</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.206887412689049</v>
+        <v>3.219409702364672</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.9438480016791928</v>
+        <v>0.956757811255244</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.154842487265014</v>
+        <v>3.167849618682617</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.633629821826908</v>
+        <v>2.646608964225372</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.746674404800345</v>
+        <v>2.759785209175284</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.7639860493563901</v>
+        <v>0.7770289456507555</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.982183928175317</v>
+        <v>1.995250182475793</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1136639657201854</v>
+        <v>-0.1004829564249476</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1510690471203091</v>
+        <v>0.1642677860750723</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.9296083572063907</v>
+        <v>0.9430134848592218</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.5780765632023943</v>
+        <v>-0.5646192694921766</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.7592381902342424</v>
+        <v>0.7726904789543525</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.641915175380547</v>
+        <v>1.655471221732149</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.408976994340108</v>
+        <v>2.532672670004288</v>
       </c>
     </row>
     <row r="12">
@@ -4220,101 +4220,101 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.785290286146989</v>
+        <v>1.797812575822611</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.129706893231642</v>
+        <v>2.142616702807693</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.935327184190058</v>
+        <v>3.94833431560766</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.554577871809784</v>
+        <v>4.567557014208248</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.238650544268175</v>
+        <v>5.251761348643115</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.091104706922714</v>
+        <v>3.104147603217079</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.517373434638202</v>
+        <v>2.530439688938678</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.561192480844475</v>
+        <v>1.574373490139713</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.9891901496744</v>
+        <v>2.002388888629163</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4055686321281371</v>
+        <v>0.4189737597809682</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.04368346969554437</v>
+        <v>-0.03022617598532662</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1285298808518576</v>
+        <v>0.004151976369996646</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.583883498456359</v>
+        <v>0.4571254339056097</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.959831819028601</v>
+        <v>2.051676423535717</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.08681</t>
+          <t>X &lt; -0.0868</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2182963375024656</v>
+        <v>0.2312061470785167</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.891096803838202</v>
+        <v>1.904103935255804</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.021349936445702</v>
+        <v>2.034329078844166</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.926537743929927</v>
+        <v>3.939648548304866</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.259546716253006</v>
+        <v>2.272612970553482</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.356273091907589</v>
+        <v>2.369454101202827</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.483243130537318</v>
+        <v>2.496441869492081</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.881238246261276</v>
+        <v>0.8946433739141071</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2187728451415225</v>
+        <v>0.1260324412178235</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3597544461496724</v>
+        <v>0.2666082912070635</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.2355372143822834</v>
+        <v>0.1417351268393929</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.7824172795451005</v>
+        <v>0.8529007446088173</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.172250829350141</v>
+        <v>1.184773119025763</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.73369774424512</v>
+        <v>0.7466075538211712</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.098359829437392</v>
+        <v>2.111366960854994</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.788730264097673</v>
+        <v>1.801709406496137</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.329487934656008</v>
+        <v>4.342598739030947</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.483372657477233</v>
+        <v>1.414166317053123</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.545481818325371</v>
+        <v>1.558548072625847</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.22514129766428</v>
+        <v>1.238322306959518</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.7236127771207421</v>
+        <v>0.7368115160755053</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.5670410422684213</v>
+        <v>-0.5536359146155903</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.1019317078661217</v>
+        <v>-0.1709655603941371</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.4266406409651182</v>
+        <v>-0.4952727323888197</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.7645687349516237</v>
+        <v>-0.833339205558417</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2845671884733534</v>
+        <v>-0.2302917876360269</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.09083134271136828</v>
+        <v>0.04433649471818057</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.745461371376479</v>
+        <v>-1.732551561800427</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3941438568686877</v>
+        <v>-0.4419296881284964</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.3155734531092662</v>
+        <v>-0.3633975211203122</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.01077878621998</v>
+        <v>0.9609179379952977</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.9988686355356293</v>
+        <v>-1.046267383152191</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.362007168458774</v>
+        <v>-1.409136549974711</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.99510308609397</v>
+        <v>-2.041998258510013</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.995890717673241</v>
+        <v>-2.042904233321508</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.352560536409683</v>
+        <v>-3.39886219067688</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.929934645704137</v>
+        <v>-2.976963142980772</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.062200956937801</v>
+        <v>-3.109113955597742</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.30818728781238</v>
+        <v>-3.35526315789474</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.567172007401822</v>
+        <v>-3.52395816233777</v>
       </c>
     </row>
     <row r="16">
@@ -4428,569 +4428,569 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1530127882950865</v>
+        <v>-0.1849976631874171</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.805182290925515</v>
+        <v>-1.836782974662007</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.302949693479256</v>
+        <v>-1.335255109716087</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.468603616378338</v>
+        <v>-1.50072338607773</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2539069630553072</v>
+        <v>-0.287429385437342</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.6789828528958992</v>
+        <v>-0.711995997533748</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.658556926086383</v>
+        <v>-1.690821256038639</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.67964718824485</v>
+        <v>-2.711361710782221</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.695674600809042</v>
+        <v>-2.727448335472388</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.414986879159486</v>
+        <v>-3.446704855270674</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.317028905543474</v>
+        <v>-3.348993029835462</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.893503674838463</v>
+        <v>-2.925845819992958</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.009931531300204</v>
+        <v>-3.042470280668873</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.058270145479682</v>
+        <v>-3.028593403079761</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.01605</t>
+          <t>X &lt; -0.01606</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.5896307049795197</v>
+        <v>-0.6117571520296821</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.233354179163541</v>
+        <v>-2.255094775568786</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.52329201100828</v>
+        <v>-1.545697037764981</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.893054548662654</v>
+        <v>-1.91517679285851</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3199710263212339</v>
+        <v>-0.3433984265620253</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5891590633402046</v>
+        <v>-0.6122993202415401</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.375420984689491</v>
+        <v>-1.398091941861608</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.873933296546767</v>
+        <v>-1.896492455329344</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.100622510731732</v>
+        <v>-2.123076725653497</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.9150468212462</v>
+        <v>-2.937342568106828</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.74780377559032</v>
+        <v>-2.770321346477225</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.340923580209555</v>
+        <v>-2.363720851380869</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.32083940626655</v>
+        <v>-2.343853638746332</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.910509290739974</v>
+        <v>-2.889628517769218</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.001639</t>
+          <t>X &lt; 0.00163</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1865</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.215483048644472</v>
+        <v>-1.256208895284082</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.894036973131612</v>
+        <v>-1.934403668616831</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.207769765570397</v>
+        <v>-2.248067538203969</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.209627507163326</v>
+        <v>-2.249981698098189</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.546255765992164</v>
+        <v>-1.58650675457347</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.021178060547591</v>
+        <v>-2.061525447221726</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.985938792390392</v>
+        <v>-3.026291341508724</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.158248112225138</v>
+        <v>-3.19851445728586</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.298390096916336</v>
+        <v>-3.338667293790458</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.692696590831453</v>
+        <v>-3.732796011065197</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.548209576615342</v>
+        <v>-3.588285473483282</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.378459417277682</v>
+        <v>-3.418568992510437</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.07370568967945</v>
+        <v>-3.113740211387871</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.063345983108249</v>
+        <v>-3.073775618806401</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.01933</t>
+          <t>X &lt; 0.01932</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.617820897668445</v>
+        <v>-1.628133265722866</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.308066740002623</v>
+        <v>-2.318415549731995</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.409992999321382</v>
+        <v>-2.420386536205868</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.34624621219929</v>
+        <v>-2.356648364764858</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.826627219761356</v>
+        <v>-1.837383961026013</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.955341257967177</v>
+        <v>-1.965984940857048</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.511639466222547</v>
+        <v>-2.522058225889474</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.594956333006046</v>
+        <v>-2.605443746748882</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.587201118887506</v>
+        <v>-2.597712435188541</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.278337880710801</v>
+        <v>-3.288725142012936</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.053323360602995</v>
+        <v>-3.063862946484974</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.859542604459953</v>
+        <v>-2.870169917243814</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.804228602974028</v>
+        <v>-2.814977631147123</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.665681595383049</v>
+        <v>-2.655230360120498</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.03702</t>
+          <t>X &lt; 0.037</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.040178304499051</v>
+        <v>-1.04785753033805</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.688508986219418</v>
+        <v>-1.696186962561256</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.591075608324282</v>
+        <v>-1.598857791260876</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.440016811135003</v>
+        <v>-1.447843333318318</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.170833930732741</v>
+        <v>-1.178854551757524</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.088371444102677</v>
+        <v>-1.096383715133413</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.624474360059821</v>
+        <v>-1.632293924784044</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.676899639053332</v>
+        <v>-1.684775962144514</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.795627805668445</v>
+        <v>-1.803471956032737</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.38819370966322</v>
+        <v>-2.395941243658193</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.216888100517828</v>
+        <v>-2.224740035895337</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.279522097335864</v>
+        <v>-2.287349184420741</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.204920947806656</v>
+        <v>-2.212847880864082</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.091615188841892</v>
+        <v>-2.084019148623945</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.05471</t>
+          <t>X &lt; 0.05469</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2811</v>
+        <v>2812</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8999539009465138</v>
+        <v>-0.9056947915963036</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.005472436185208</v>
+        <v>-1.011365579688835</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.7436793640798243</v>
+        <v>-0.749714457697884</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5589220835546698</v>
+        <v>-0.5650112279824384</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4045026229447117</v>
+        <v>-0.4107124658931696</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.4779356245340196</v>
+        <v>-0.4840887109205028</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7563766976757194</v>
+        <v>-0.7624445206381409</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.9559211316705216</v>
+        <v>-0.9619759643798673</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.962160150392279</v>
+        <v>-0.9682235213545738</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.5088177106826</v>
+        <v>-1.514789298676469</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.303277917991963</v>
+        <v>-1.309349975748212</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.498196173949729</v>
+        <v>-1.504198690831906</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.685610876301169</v>
+        <v>-1.691599324394431</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.629778315681449</v>
+        <v>-1.624128568058737</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0724</t>
+          <t>X &lt; 0.07238</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9375916120540566</v>
+        <v>-0.9419507391132598</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.09059515728957</v>
+        <v>-1.095050043676792</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8781172834941913</v>
+        <v>-0.8826795371867746</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7302832448682395</v>
+        <v>-0.7348850084882272</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6935521659875405</v>
+        <v>-0.698216606385138</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.001682900005392</v>
+        <v>-1.006222464807948</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.331375946491818</v>
+        <v>-1.335817554578242</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.387080696371378</v>
+        <v>-1.391548339259991</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.266216726000579</v>
+        <v>-1.270732139068379</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.572991941560453</v>
+        <v>-1.577485223441357</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.529798944146116</v>
+        <v>-1.534327393981222</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.707529986882221</v>
+        <v>-1.711999646618203</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.879663424150081</v>
+        <v>-1.884116782902211</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.809289259529869</v>
+        <v>-1.804791326388127</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.09009</t>
+          <t>X &lt; 0.09006</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3245</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7438987253665132</v>
+        <v>-0.7620701127934097</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.050053382360595</v>
+        <v>-1.067846673797753</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9986521385423188</v>
+        <v>-0.9856450071247167</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.220625971065019</v>
+        <v>-1.207646828666554</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.9129657474352442</v>
+        <v>-0.8998549430603049</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9678155149225418</v>
+        <v>-0.9547726186281764</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.405057598963076</v>
+        <v>-1.3919913446626</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.271413473012856</v>
+        <v>-1.258232463717619</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.377369940602065</v>
+        <v>-1.364171201647302</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.533790553809077</v>
+        <v>-1.520385426156246</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.506234808416686</v>
+        <v>-1.492777514706468</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.670566721139721</v>
+        <v>-1.657114432419611</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.765937335652836</v>
+        <v>-1.752381289301233</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.745831308025522</v>
+        <v>-1.72544430273755</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.1078</t>
+          <t>X &lt; 0.1077</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3396</v>
+        <v>3397</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7187243278368385</v>
+        <v>-0.7213852387454978</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.935997848667192</v>
+        <v>-0.9386846991335247</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.256558068593833</v>
+        <v>-1.259173977836781</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.345552345683579</v>
+        <v>-1.348136477473979</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.075449603292753</v>
+        <v>-1.078144024730783</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.026587983109728</v>
+        <v>-1.029281949899477</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.389433948750671</v>
+        <v>-1.392027478983991</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.311847827675315</v>
+        <v>-1.314491289750308</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.298207703251066</v>
+        <v>-1.300860027225021</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.426590148254427</v>
+        <v>-1.429252959097191</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.409323155177617</v>
+        <v>-1.412003825920607</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.594225142287478</v>
+        <v>-1.596851051271543</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.851203393504242</v>
+        <v>-1.853778327245692</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.820912841452873</v>
+        <v>-1.817975871197518</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.1255</t>
+          <t>X &lt; 0.1254</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3511</v>
+        <v>3512</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.7624508060215547</v>
+        <v>-0.7646039737967598</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.7130164747581134</v>
+        <v>-0.7152576287060057</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.064332655670881</v>
+        <v>-1.066493150703486</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.259715550332878</v>
+        <v>-1.261815883220287</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9875941767809451</v>
+        <v>-0.9897973327994904</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9590012147556948</v>
+        <v>-0.9612002518618254</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.085334816743789</v>
+        <v>-1.087503005661567</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.167641898867608</v>
+        <v>-1.169809065240855</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.042636414742262</v>
+        <v>-1.044843102961792</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.137660351584692</v>
+        <v>-1.139879794074126</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.156034623932946</v>
+        <v>-1.158259369389782</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.362151788912549</v>
+        <v>-1.364317561475836</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.595936619860339</v>
+        <v>-1.598056160508413</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.501422255077692</v>
+        <v>-1.499013943783346</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.1432</t>
+          <t>X &lt; 0.1431</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3615</v>
+        <v>3616</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4537470302430506</v>
+        <v>-0.4555646940780278</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5345680401497006</v>
+        <v>-0.5364240640612437</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9422413678458383</v>
+        <v>-0.9440006106416163</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.155834403715041</v>
+        <v>-1.157530879933084</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8517573315070166</v>
+        <v>-0.8535586075157227</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.9258151753561563</v>
+        <v>-0.9275859632806558</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.023336084343185</v>
+        <v>-1.025084073602585</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.089063530510089</v>
+        <v>-1.090811693045353</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.9693801403470772</v>
+        <v>-0.9711645948875898</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.003187518343658</v>
+        <v>-1.00499522534647</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.8334050600594054</v>
+        <v>-0.8352682961187554</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.087812337539511</v>
+        <v>-1.089604992656113</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.10564543111682</v>
+        <v>-1.107449801773399</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.006530287410769</v>
+        <v>-1.004628070821866</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3714</v>
+        <v>3715</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4140178748115346</v>
+        <v>-0.415465386757532</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4818235273771236</v>
+        <v>-0.4833014796486168</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.8354511095694832</v>
+        <v>-0.8368466699205825</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.9861688605467762</v>
+        <v>-0.9875208479863318</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.8118897106856622</v>
+        <v>-0.8133052647993253</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7148518140738318</v>
+        <v>-0.7162853494126864</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8119758148799932</v>
+        <v>-0.8133865527038893</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9152120726166189</v>
+        <v>-0.9166097550246732</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.8002917351291288</v>
+        <v>-0.8017228972635166</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.801997546286259</v>
+        <v>-0.8034543845988793</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.6959433238119317</v>
+        <v>-0.6974355887279415</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.8349771581316574</v>
+        <v>-0.8364317948838718</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.8634662126887775</v>
+        <v>-0.8649265300446558</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.7064210227019316</v>
+        <v>-0.7049282173219424</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3780</v>
+        <v>3781</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2656502896273167</v>
+        <v>-0.2668938903129501</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2020583466763384</v>
+        <v>-0.2033597033503582</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.477195332464035</v>
+        <v>-0.4784346897878251</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.8076222301184686</v>
+        <v>-0.8087718150418297</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6193181864740822</v>
+        <v>-0.6205315854067237</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5187377243297533</v>
+        <v>-0.5199708557630771</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.5891878743825529</v>
+        <v>-0.5904051873015561</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7251229497019835</v>
+        <v>-0.7263167492134173</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5603797973239395</v>
+        <v>-0.5616192897451526</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.5768202191411405</v>
+        <v>-0.5780773976316738</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5025630151074978</v>
+        <v>-0.5038456366406692</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.585637330189094</v>
+        <v>-0.5868978043049751</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6473470107429407</v>
+        <v>-0.6486024204302012</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.4621714650436459</v>
+        <v>-0.4609513734083919</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3846</v>
+        <v>3847</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.2000980766235614</v>
+        <v>-0.201123284420369</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1133063862587278</v>
+        <v>-0.1143876898070459</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3126885215442172</v>
+        <v>-0.3137268002142903</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5833204532214182</v>
+        <v>-0.5842864254337741</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4592808882536517</v>
+        <v>-0.4602906149559942</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3552876355836645</v>
+        <v>-0.3563187520386961</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3740324301596232</v>
+        <v>-0.3750609625928334</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4636661643327002</v>
+        <v>-0.4646815883974966</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3806258381711345</v>
+        <v>-0.3816646116640854</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3593632574981243</v>
+        <v>-0.3604256150995937</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3158146109883972</v>
+        <v>-0.3168930543392534</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.3188632136000678</v>
+        <v>-0.319940713377008</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4386433883803775</v>
+        <v>-0.4396989923305767</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3303090476898163</v>
+        <v>-0.3293230980928641</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3915</v>
+        <v>3916</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0494464668494814</v>
+        <v>-0.05027210078123545</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.05847164207405342</v>
+        <v>0.05759237742014989</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1697736606572207</v>
+        <v>-0.1706015450224356</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3568886536601354</v>
+        <v>-0.357667213465831</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1425033603598607</v>
+        <v>-0.1433455611726586</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.08600826298019371</v>
+        <v>-0.08686052431109204</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1058453462592155</v>
+        <v>-0.1066943341600037</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.04903244431245923</v>
+        <v>-0.04990382957515749</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.0060680499787793</v>
+        <v>0.005181200604873482</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.0134295280481922</v>
+        <v>-0.01432547678407303</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1273047973775832</v>
+        <v>-0.1281754183136314</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.1041161517761608</v>
+        <v>-0.104992577447824</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2035995923975165</v>
+        <v>-0.2044578105741977</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1437989052917814</v>
+        <v>-0.1430617262586082</v>
       </c>
     </row>
     <row r="31">
@@ -5208,257 +5208,257 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3959</v>
+        <v>3960</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.02418504333484606</v>
+        <v>0.02348870140625081</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1886168756900375</v>
+        <v>0.187857594428003</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.03412439801255118</v>
+        <v>0.03339846344230324</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1242256427138386</v>
+        <v>-0.1249103295003735</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.05666901969999572</v>
+        <v>0.05593131872296908</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1663027188832373</v>
+        <v>0.1655409504842069</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.0953806278095044</v>
+        <v>0.09463525591143451</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1212087602082264</v>
+        <v>0.1204503512833952</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.2002905422047263</v>
+        <v>0.1995110177726218</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.09591953692168431</v>
+        <v>0.09515474315455918</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1072615100570857</v>
+        <v>0.1064907785828098</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1558798766441711</v>
+        <v>0.1550969561226268</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1034030179758787</v>
+        <v>0.1026274115206931</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.08961530169639076</v>
+        <v>0.09016946202876142</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.2493</t>
+          <t>X &lt; 0.2492</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.002157802023631916</v>
+        <v>-0.002709305752283342</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.2184368582536322</v>
+        <v>0.2178131728642043</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.08636063640066283</v>
+        <v>0.08576541514540992</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.0689543583226353</v>
+        <v>-0.06950978051759193</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.104420105694679</v>
+        <v>0.1038155102122502</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.240977151623845</v>
+        <v>0.2403413486822714</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.269729358487325</v>
+        <v>0.269085193765541</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.2904334241081941</v>
+        <v>0.2897788652086604</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.3181636820408968</v>
+        <v>0.3175012561669064</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2559390431974293</v>
+        <v>0.2552828658040838</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2400792223801034</v>
+        <v>0.2394245356862044</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.3135626748837836</v>
+        <v>0.312889693420658</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2822529869307999</v>
+        <v>0.2815830710699032</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.2962698770017838</v>
+        <v>0.2966571272870482</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.267</t>
+          <t>X &lt; 0.2669</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4024</v>
+        <v>4025</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.07827854810197721</v>
+        <v>-0.07873673385282132</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2061872739615396</v>
+        <v>0.2056437272811849</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.0973932140086049</v>
+        <v>0.09687277509574699</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.03150157756491012</v>
+        <v>-0.03198913304242978</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1626182750370049</v>
+        <v>0.1620774514998899</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.3001075011944607</v>
+        <v>0.2995350455707211</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2538036311773766</v>
+        <v>0.2532416255242396</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2717192756050437</v>
+        <v>0.2711483019739234</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2989383626608202</v>
+        <v>0.2983598157224208</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2818624482757386</v>
+        <v>0.2812801072216828</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2152654466351152</v>
+        <v>0.2146975000914182</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.263680811566914</v>
+        <v>0.2631008927006562</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2798256291810972</v>
+        <v>0.2792375872617328</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.3448909225356331</v>
+        <v>0.3452042822809744</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.2847</t>
+          <t>X &lt; 0.2846</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4047</v>
+        <v>4048</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.005753591145932546</v>
+        <v>-0.006156119182463726</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1694399022532096</v>
+        <v>0.1689816202441818</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.009730005867417901</v>
+        <v>0.009307817096399162</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.06841971815666881</v>
+        <v>-0.06882184923997414</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1215370765810775</v>
+        <v>0.1210837730440488</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.210601600190401</v>
+        <v>0.210128419466848</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1887246190761616</v>
+        <v>0.1882559621261208</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.203871362194711</v>
+        <v>0.2033951452287823</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2305729555935443</v>
+        <v>0.2300894599708698</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2087504357698577</v>
+        <v>0.2082655339538917</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1413507903183344</v>
+        <v>0.140880719652742</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.214365647611011</v>
+        <v>0.2138775944085651</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2774258550421891</v>
+        <v>0.2769187500960086</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.3188303352316879</v>
+        <v>0.3190890931223009</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.3024</t>
+          <t>X &lt; 0.3023</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01673405341252732</v>
+        <v>-0.0170768542656603</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1505681502204155</v>
+        <v>0.1501735017083448</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.0634167105726533</v>
+        <v>0.06304064420994138</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.01074059099617841</v>
+        <v>0.01037813180040104</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1974986513531221</v>
+        <v>0.1970866220167551</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2875027170760376</v>
+        <v>0.2870703778521033</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2162508538070966</v>
+        <v>0.2158352541042348</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2292717270363056</v>
+        <v>0.2288496431027696</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.280161716929598</v>
+        <v>0.279726536576149</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2546872287568362</v>
+        <v>0.2542524703653015</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.16210901166653</v>
+        <v>0.1616954498083629</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2349579942658906</v>
+        <v>0.2345265619601946</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2712894573822382</v>
+        <v>0.2708461028961011</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.3136148642482155</v>
+        <v>0.3138275878019812</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_30.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_30.xlsx
@@ -568,1509 +568,1509 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.2017</t>
+          <t>X ≈ -0.2014</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.846583499326243</v>
+        <v>-7.033305332546249</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>17.28548974534039</v>
+        <v>14.0472576553231</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>12.14679910256503</v>
+        <v>9.124622218383443</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7.529464293968957</v>
+        <v>4.722086356307138</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>16.49703901752626</v>
+        <v>17.84138944199611</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>12.04560460542365</v>
+        <v>13.58173870017708</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.96401932844195</v>
+        <v>13.52453571880672</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>6.745825154996346</v>
+        <v>8.524063804285255</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11.44272528411516</v>
+        <v>13.02920736365868</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>15.35346923418861</v>
+        <v>16.75017315495622</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.39424199295348</v>
+        <v>12.00812333229142</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.9119310499563724</v>
+        <v>2.982657248328437</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>5.252818642849675</v>
+        <v>7.132648148872221</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.00358937544868</v>
+        <v>16.47428943371664</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.184</t>
+          <t>X ≈ -0.1838</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.241909649469676</v>
+        <v>-3.926154574045007</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-9.618830302969812</v>
+        <v>-8.353990608967713</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.065623703155104</v>
+        <v>2.648486065686534</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.34594090215289</v>
+        <v>-2.921403260470214</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.112497476288389</v>
+        <v>-3.410293413340497</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.9562882399010704</v>
+        <v>-0.2871407991965071</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.900949999674495</v>
+        <v>-3.199915257612552</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.4059708327257354</v>
+        <v>-0.812822943429012</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.11957893025145</v>
+        <v>2.003739209424552</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.278945087262521</v>
+        <v>-4.527585988885996</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.7086669765657234</v>
+        <v>-1.877740739715101</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-9.003762261855087</v>
+        <v>-10.38733398140732</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.094821783788028</v>
+        <v>-2.215699666978288</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.647204275343711</v>
+        <v>-4.824411864984668</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.1663</t>
+          <t>X ≈ -0.1661</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>35</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10.34233070128347</v>
+        <v>10.31332727591053</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.89040816202845</v>
+        <v>5.889272415713151</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.347001568672404</v>
+        <v>8.346913112463291</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.32909214463691</v>
+        <v>11.32867764074061</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10.79486219953713</v>
+        <v>10.84336165163216</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>8.243175983035719</v>
+        <v>8.267128034952407</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.3956017248950232</v>
+        <v>-0.3476811400092146</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.714796024225485</v>
+        <v>-3.66564309344971</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.92301508318468</v>
+        <v>-0.8498592330279351</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.936077813848151</v>
+        <v>4.035330680514569</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.442412969672674</v>
+        <v>9.542261235894031</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>20.90190386555788</v>
+        <v>21.02556410742691</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>20.4870551152781</v>
+        <v>20.63571962050779</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>17.86073223259023</v>
+        <v>18.0327309921582</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.1487</t>
+          <t>X ≈ -0.1485</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>63</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.482043681729252</v>
+        <v>1.452965092849759</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.870663019714776</v>
+        <v>-4.871888591600694</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.065311568938675</v>
+        <v>1.065169080993208</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3876963248379397</v>
+        <v>-0.3881906449006252</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.9248137563875858</v>
+        <v>-0.8763892133534483</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.212039236407783</v>
+        <v>-2.188146027448347</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.040926128460519</v>
+        <v>4.088866605245066</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.160626502557577</v>
+        <v>5.209814783662196</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.856894168729468</v>
+        <v>9.930085983621616</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.424481348955602</v>
+        <v>7.52374211235712</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.049550668770316</v>
+        <v>4.149386335887023</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.498356366977987</v>
+        <v>2.621990047888531</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.252727727762007</v>
+        <v>5.401381042440271</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.892478264337562</v>
+        <v>2.47717543660336</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.131</t>
+          <t>X ≈ -0.1308</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.855139997508104</v>
+        <v>3.034744075323026</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.649114277940868</v>
+        <v>8.38098231872749</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.323843482990263</v>
+        <v>3.834915494268451</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.988230067211859</v>
+        <v>2.580313913719266</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.919181187725854</v>
+        <v>3.478571047278798</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.282243111144538</v>
+        <v>0.9800319953083019</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.601804718912511</v>
+        <v>3.692515356115777</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.200473639524027</v>
+        <v>1.841783043834191</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.6714189205261434</v>
+        <v>0.4182013732556911</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.291492428761131</v>
+        <v>-0.4047887417637739</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.790521557029109</v>
+        <v>-6.160147071658628</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.757480112602252</v>
+        <v>-4.715513633336798</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.238365064471616</v>
+        <v>-2.334752242958537</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.9279591233478328</v>
+        <v>0.6914611508877186</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.1134</t>
+          <t>X ≈ -0.1132</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.519297082446791</v>
+        <v>-2.00876688270305</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.810644421059521</v>
+        <v>5.295611462493987</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.412045649655774</v>
+        <v>6.878265591066096</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.53664774251819</v>
+        <v>9.972265533290468</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>12.98596177061307</v>
+        <v>12.45004684972562</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>10.29329311448015</v>
+        <v>11.73806504592682</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.218574690123738</v>
+        <v>5.751075452727029</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.737370740473807</v>
+        <v>7.264778702650503</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.675571259611473</v>
+        <v>8.218565982090965</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.18302396201122</v>
+        <v>1.46343046085849</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.605196886617918</v>
+        <v>4.227805600790923</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.357745003481462</v>
+        <v>-0.660907127476726</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.217835289197168</v>
+        <v>-3.035857249725382</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5750179468772387</v>
+        <v>0.1826602708003406</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.09565</t>
+          <t>X ≈ -0.09557</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.267355174012643</v>
+        <v>-1.266421745580899</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-6.158592362739341</v>
+        <v>-6.139664134489564</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-4.920167798763934</v>
+        <v>-4.886700686601699</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-6.426290819705692</v>
+        <v>-5.582618805962653</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4227519899160015</v>
+        <v>0.5229489202466908</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.6932739999700317</v>
+        <v>-0.02869497455047565</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.426161923176807</v>
+        <v>1.560812968889437</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.05025456035964</v>
+        <v>5.221802925680585</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.170929615948801</v>
+        <v>4.361023022057566</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.4947779179493</v>
+        <v>1.888372421007098</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6495060975107378</v>
+        <v>0.03338584878017059</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.146482330291988</v>
+        <v>0.0915062553535364</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.9130127853165035</v>
+        <v>-1.12977789424675</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.146293528532588</v>
+        <v>-3.360421310085208</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.07796</t>
+          <t>X ≈ -0.07791</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.525843742702641</v>
+        <v>2.056074040406564</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.585708785135516</v>
+        <v>1.738923653512927</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.861002392210928</v>
+        <v>2.007639418318561</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.982785880161849</v>
+        <v>0.8111305965213589</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.804872731374942</v>
+        <v>4.976726660822557</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.610501346167005</v>
+        <v>-2.381477527800108</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.990056536944536</v>
+        <v>-1.115161871257072</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.798089550202675</v>
+        <v>-2.562689348330949</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.54278645954421</v>
+        <v>-5.566664136343846</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.723005179713603</v>
+        <v>-6.037430351772983</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.231387955411492</v>
+        <v>-1.872506806225189</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.210432621848113</v>
+        <v>-4.104425721234271</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.301724414758681</v>
+        <v>-5.167157326323313</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.075988764532148</v>
+        <v>-4.919649960222607</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.06027</t>
+          <t>X ≈ -0.06026</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.814489791282156</v>
+        <v>-4.217110782213496</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-10.19925849809253</v>
+        <v>-10.15867220656884</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-9.10713237498576</v>
+        <v>-8.62553965439902</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.711495749463033</v>
+        <v>-7.531946962453361</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-10.46952400382421</v>
+        <v>-10.43826993286558</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-9.412098808560565</v>
+        <v>-9.685495911512227</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-11.48914896481414</v>
+        <v>-11.89870390121714</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-13.18534990656182</v>
+        <v>-13.81570899719311</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-11.48193189554286</v>
+        <v>-12.404759139962</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-13.0571481793509</v>
+        <v>-14.19928581373</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-12.48385047502791</v>
+        <v>-13.43805795384151</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-11.95195988486175</v>
+        <v>-12.897207062764</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-11.87459830036421</v>
+        <v>-13.01966134311564</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-14.63393727700335</v>
+        <v>-15.67327314862855</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.04258</t>
+          <t>X ≈ -0.0426</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>284</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.9052333279619944</v>
+        <v>-0.7667811608582085</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.171839717867783</v>
+        <v>-2.011875424211574</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.13476083229704</v>
+        <v>-4.166162001870646</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.060873716877452</v>
+        <v>-5.093104609938877</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.190712565747802</v>
+        <v>-4.334687910488427</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3320135765632699</v>
+        <v>0.1623735820209973</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.569598191153688</v>
+        <v>-2.716044826843586</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.797230215222037</v>
+        <v>-4.944700859378116</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.858212371744813</v>
+        <v>-4.982103924109126</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.595455111736555</v>
+        <v>-3.697453390629391</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.504381622109513</v>
+        <v>-4.606034418075389</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.357327413416073</v>
+        <v>-2.435299238270993</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.073252914616887</v>
+        <v>-2.127953635099054</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.495404588334019</v>
+        <v>-1.323405828767356</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.0249</t>
+          <t>X ≈ -0.02495</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>322</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.170357024323174</v>
+        <v>-2.196931100390216</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.781543117387073</v>
+        <v>-3.7792621859588</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.312960464874891</v>
+        <v>-2.312033721916166</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.424971346131322</v>
+        <v>-3.425465838509325</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5471118309040364</v>
+        <v>-0.4985659111382645</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2497378012688714</v>
+        <v>-0.2257803923192583</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3344481605351177</v>
+        <v>-0.2864364815447971</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.061837232945294</v>
+        <v>1.111084795339011</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.06917805778891761</v>
+        <v>0.142435167568614</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.091299744752192</v>
+        <v>-0.9919524194576184</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6748828905899558</v>
+        <v>-0.5749748545712805</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.3299457320235248</v>
+        <v>-0.2062491109952802</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1815804332966806</v>
+        <v>0.3302699810745082</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.38771497237741</v>
+        <v>-2.215716212810747</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.007215</t>
+          <t>X ≈ -0.007296</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.796705504218501</v>
+        <v>-3.575387800060021</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.671049492019236</v>
+        <v>-0.3935477237841596</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-5.013189297826848</v>
+        <v>-4.766606076971783</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.567174680554274</v>
+        <v>-3.428760894278142</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-6.473885286281543</v>
+        <v>-6.570529929129265</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-7.755458625067632</v>
+        <v>-7.889256346649915</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-9.419116352754791</v>
+        <v>-9.541424372214841</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-8.307237628120475</v>
+        <v>-8.415745196258662</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-8.105061889906409</v>
+        <v>-8.187465816005535</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.849717528341536</v>
+        <v>-6.889278481701155</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.791260791864886</v>
+        <v>-6.828166939847264</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-7.546356323720026</v>
+        <v>-7.565756170652136</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-6.124401913875602</v>
+        <v>-6.104150171486573</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.793403105754336</v>
+        <v>-3.733089394351907</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.01047</t>
+          <t>X ≈ 0.01035</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.623773173391626</v>
+        <v>-3.666820836399495</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.377816409312466</v>
+        <v>-4.535870029229478</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.344016365496074</v>
+        <v>-3.634754171084815</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.928076936193492</v>
+        <v>-3.220779220779292</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-3.180652203574972</v>
+        <v>-3.141846543549264</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.45470674536832</v>
+        <v>-1.448606479275853</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1748686096512273</v>
+        <v>0.195282886044204</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5649428230073426</v>
+        <v>0.5817228529335239</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.361103523627357</v>
+        <v>1.397022971069518</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.9173867012738697</v>
+        <v>-0.8472601552000683</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.2649450023911939</v>
+        <v>-0.1991278754635672</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.05514743567847091</v>
+        <v>0.1431297709923669</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.222146274777856</v>
+        <v>-1.104300882844186</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4249820531227471</v>
+        <v>-0.2870742026469344</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.02816</t>
+          <t>X ≈ 0.02801</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>319</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.004977386393584</v>
+        <v>3.289261215865373</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.647709788627523</v>
+        <v>2.646523002182832</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.133816146819157</v>
+        <v>4.44714238063932</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.89100053805646</v>
+        <v>5.20398566950297</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.412272113487482</v>
+        <v>3.774297657077561</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.963564638420337</v>
+        <v>5.301001671194371</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.565374655329684</v>
+        <v>4.92686595814439</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.72526525919185</v>
+        <v>5.087992445409988</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.723844231195791</v>
+        <v>4.110580964799794</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.814364306339243</v>
+        <v>4.227191255458237</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.609663148079022</v>
+        <v>4.023050807922182</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.763163557487601</v>
+        <v>2.200339802340331</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.969971951823119</v>
+        <v>2.432141123425403</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.88222797822521</v>
+        <v>2.367706361616285</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.04584</t>
+          <t>X ≈ 0.04566</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>278</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3967818111923052</v>
+        <v>0.007873786623804335</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.260415862013296</v>
+        <v>5.618941305784539</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>7.023917858553219</v>
+        <v>7.023764468548897</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>7.51385523235745</v>
+        <v>7.513360739979447</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>6.615853449045915</v>
+        <v>6.664399368811686</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.114666327601832</v>
+        <v>4.778911506335653</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7.188229349630674</v>
+        <v>6.876528798405204</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>5.642024015196448</v>
+        <v>5.691271577590207</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>6.660178549321159</v>
+        <v>6.373723428885015</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>6.529684213422904</v>
+        <v>6.269319308501693</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>7.044407515594408</v>
+        <v>6.784603321397299</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>5.639936747086381</v>
+        <v>5.403921137898834</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.061512512478046</v>
+        <v>2.850489830040047</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.567823702272932</v>
+        <v>2.38011023162381</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.06354</t>
+          <t>X ≈ 0.06331</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.389212973765744</v>
+        <v>-1.194322351202722</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.127036621414717</v>
+        <v>-2.777499436358575</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.521808006169856</v>
+        <v>-3.171237424673329</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.828264085288879</v>
+        <v>-3.479949874686717</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.239916083799464</v>
+        <v>-4.84639199809483</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.435991835823721</v>
+        <v>-7.643781917872346</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-8.39406464050473</v>
+        <v>-8.143034498325925</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-6.677727170754352</v>
+        <v>-6.854481293796937</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.991984436447439</v>
+        <v>-4.259874955565309</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.348453451117905</v>
+        <v>-2.013528097783805</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.299879500207794</v>
+        <v>-3.972054510232176</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-4.265501347852471</v>
+        <v>-3.913887772867284</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.248970978458459</v>
+        <v>-3.870449208203041</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.023235328231927</v>
+        <v>-3.621404346187674</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.08122</t>
+          <t>X ≈ 0.08096</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.930848675347939</v>
+        <v>1.677080293339529</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.6607295745785748</v>
+        <v>0.09390320818376807</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.526089194627616</v>
+        <v>-1.777667292446154</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-8.278216992215839</v>
+        <v>-7.559113300492619</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.914545760997754</v>
+        <v>-3.12225406706024</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1857991823431178</v>
+        <v>0.5988073138275922</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.231293855334769</v>
+        <v>-1.924902962589982</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7330100498980983</v>
+        <v>1.057540139095636</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.759344655644341</v>
+        <v>-2.920319169548598</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.6680869813859047</v>
+        <v>-0.2958718882945632</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.8727881396460972</v>
+        <v>-0.5000123358306539</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.8384099872907242</v>
+        <v>-0.4418455984657612</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.212027394689926</v>
+        <v>0.6408289872857367</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.5426291119462832</v>
+        <v>-0.09534782557580002</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.09888</t>
+          <t>X ≈ 0.09859</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1506629168340652</v>
+        <v>0.4310646457012837</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.828950507980771</v>
+        <v>1.462266645512642</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-7.118452455721716</v>
+        <v>-7.42820336894578</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-4.683940242763775</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-5.826784154957529</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.623879677699151</v>
+        <v>-3.593214322413111</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.392800563281099</v>
+        <v>-2.346680869154902</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.517763943909955</v>
+        <v>-3.466108400780072</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.05283284693576462</v>
+        <v>-0.8887019249494514</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5187035242900393</v>
+        <v>-0.4053409632809206</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.3140023660298468</v>
+        <v>-0.6094814108170112</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.3095142184570037</v>
+        <v>-1.204909444693904</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.019138755980869</v>
+        <v>-4.868041227466954</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.793403105754294</v>
+        <v>-4.61899636545148</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.1166</t>
+          <t>X ≈ 0.1162</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.046133421838704</v>
+        <v>-3.387304807343128</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>5.907897876401819</v>
+        <v>5.555833896974704</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.643561274255426</v>
+        <v>4.28490292620387</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.295525548278619</v>
+        <v>0.9060150375939884</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.626801212574229</v>
+        <v>3.048344844010487</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.054610024817961</v>
+        <v>2.443937380373228</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.926421404682287</v>
+        <v>8.523632168340789</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.111526673939018</v>
+        <v>3.671834495676755</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.52880538698146</v>
+        <v>7.14363381636452</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.41801702543421</v>
+        <v>8.074191200461868</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.34375064978272</v>
+        <v>6.992857770469676</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.508563584746689</v>
+        <v>6.173831525378283</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.957977948824634</v>
+        <v>6.655866581270644</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.922844033833719</v>
+        <v>8.659297408198192</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.1343</t>
+          <t>X ≈ 0.1339</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>10.01908396946559</v>
+        <v>11.04129004427185</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.523282491786432</v>
+        <v>5.719795202106688</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.205434183954466</v>
+        <v>3.456898335287271</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.374120866004368</v>
+        <v>2.652202937249655</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.758908235985551</v>
+        <v>3.097533235550031</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.2101284194668906</v>
+        <v>-0.3679990026402891</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.08695652173914</v>
+        <v>1.440503786638871</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.581426339490854</v>
+        <v>1.90925046550786</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.520444182968077</v>
+        <v>1.872277856371021</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.555140771253605</v>
+        <v>3.85218759331309</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>10.08120884376264</v>
+        <v>10.19010322054331</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.192510073041099</v>
+        <v>8.379111079403636</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>15.46466691203533</v>
+        <v>15.46058866685845</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>15.6904025622618</v>
+        <v>15.70963352887382</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.152</t>
+          <t>X ≈ 0.1515</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.054437504819241</v>
+        <v>1.174098701428861</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.463453431957376</v>
+        <v>-0.4090783837270493</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.088884067404415</v>
+        <v>2.355078364800406</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.239311231194733</v>
+        <v>4.590225563909712</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.6606176376951183</v>
+        <v>-0.1095498928316161</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>7.018597727936147</v>
+        <v>7.531656678618887</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.933887368670035</v>
+        <v>7.471000589393363</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.456717714782236</v>
+        <v>4.899904671115287</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.39573555825946</v>
+        <v>4.862932061978547</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>6.566018782131621</v>
+        <v>6.144366639058241</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.341115603669465</v>
+        <v>3.834963033627474</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.415897796428773</v>
+        <v>8.103656086781847</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.995746943115364</v>
+        <v>7.708498160218063</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>10.24168461354403</v>
+        <v>10.06280618012818</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.1696</t>
+          <t>X ≈ 0.1693</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>66</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>8.125144575526257</v>
+        <v>8.095948781173625</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>15.60486757337152</v>
+        <v>18.63398381722985</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>19.75555073407103</v>
+        <v>21.27054885921821</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>9.279715271598775</v>
+        <v>10.79437229437242</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>10.2565772336545</v>
+        <v>11.82027466857198</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>10.55395126328969</v>
+        <v>9.06275715708783</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>11.98439241917495</v>
+        <v>10.51725258301393</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>10.00217226023673</v>
+        <v>10.05141982263059</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>12.97149313401702</v>
+        <v>13.04475024379672</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>12.12157433768716</v>
+        <v>12.22092166298184</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>10.40172166427539</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>13.46640284693378</v>
+        <v>13.59009946796207</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.53110047846889</v>
+        <v>11.67979002624664</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>13.27198764384686</v>
+        <v>13.44398640341361</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.1874</t>
+          <t>X ≈ 0.1869</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.579690030071667</v>
+        <v>3.372241116289487</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.998806967310912</v>
+        <v>3.259652266427793</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>9.149490128010413</v>
+        <v>7.277678983995401</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>10.34873949579827</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8.741425718503081</v>
+        <v>6.918313884258161</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>9.038799748138167</v>
+        <v>8.661687638371163</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11.98439241917502</v>
+        <v>11.54220801973398</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>14.54762680569136</v>
+        <v>14.01755172993887</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.941190103714007</v>
+        <v>9.568814414919721</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>12.12157433768716</v>
+        <v>11.68616230469299</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>10.01143362186276</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>14.98155436208538</v>
+        <v>14.48136506511002</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.53110047846889</v>
+        <v>11.14503066795796</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>7.211381583240879</v>
+        <v>6.982310824090966</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.2051</t>
+          <t>X ≈ 0.2046</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>8.388649186856988</v>
+        <v>11.66899265272496</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>9.676013818430796</v>
+        <v>14.56342750786761</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.831967071356971</v>
+        <v>12.67715220612007</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>14.29957356076758</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>17.56883019808144</v>
+        <v>16.7953990466813</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>14.96765350307892</v>
+        <v>17.0681845655003</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14.88294314381271</v>
+        <v>17.00752847627477</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>23.11152667393898</v>
+        <v>24.0043822830556</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>21.60126915509737</v>
+        <v>20.98233504705318</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>19.30207499644871</v>
+        <v>20.15850646623819</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>12.49167945153792</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.88537517894964</v>
+        <v>12.54984618890281</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12.9144996879551</v>
+        <v>13.64722557577188</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.91119581092152</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.2228</t>
+          <t>X ≈ 0.2222</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.609993060374741</v>
+        <v>-0.3361987814087257</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>11.81698878549273</v>
+        <v>4.60236326387021</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>18.24039921891944</v>
+        <v>10.73036440599029</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>20.64335163523514</v>
+        <v>17.38198757763975</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>17.83233480941221</v>
+        <v>19.06665148016615</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>22.67516338450174</v>
+        <v>19.33943699898495</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>18.04499847978113</v>
+        <v>14.9309548228031</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>15.30520256326718</v>
+        <v>14.46512206241976</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>17.51694767947161</v>
+        <v>18.77597554023941</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.848847064959898</v>
+        <v>9.256494785511393</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>21.00778227033607</v>
+        <v>17.74800651188833</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>23.31488769541867</v>
+        <v>22.15399933620976</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>27.44019138755971</v>
+        <v>26.10666749660239</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>20.84774521960448</v>
+        <v>19.83397322818305</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.2404</t>
+          <t>X ≈ 0.2399</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>0.9782602681362675</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>6.371827369026896</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.036936015456334</v>
+        <v>5.97808938071222</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.167161159044667</v>
+        <v>6.1079734219269</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.628871605949001</v>
+        <v>5.61872428097498</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>7.307198016536439</v>
+        <v>8.21709119514275</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16.7462971810798</v>
+        <v>17.45876068731263</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>16.27922853729306</v>
+        <v>16.99292792692929</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>11.45634161886551</v>
+        <v>12.30479252709483</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>15.36832758444042</v>
+        <v>16.13212673697751</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.78267404522785</v>
+        <v>13.60240489409259</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>15.19800457853558</v>
+        <v>15.98615302680631</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>17.15880610617457</v>
+        <v>17.91657649559134</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>19.76549413735346</v>
+        <v>22.81678414830437</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.2581</t>
+          <t>X ≈ 0.2575</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>23</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-13.35048124792571</v>
+        <v>-17.72750312923481</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.918189080119923</v>
+        <v>-6.267201953521038</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.034865622081504</v>
+        <v>2.034712232077183</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.512916852626454</v>
+        <v>6.5124223602485</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>10.32245338648728</v>
+        <v>10.37099930625298</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>10.61982741612236</v>
+        <v>10.64378482507198</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-2.508361204013433</v>
+        <v>-2.460349525023112</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.975429847800172</v>
+        <v>-2.926182285406455</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.03641200432282</v>
+        <v>-2.963154894543251</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.809321373260232</v>
+        <v>4.908668698554877</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-4.091031958913</v>
+        <v>-3.991123922894324</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-8.4044798935142</v>
+        <v>-3.932957185529375</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1289785729145052</v>
+        <v>4.367537061819853</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.792409251225074</v>
+        <v>8.964408010791736</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.2758</t>
+          <t>X ≈ 0.2752</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>12.73647527381353</v>
+        <v>14.15655484177967</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-6.266015167076439</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-15.35643872574452</v>
+        <v>-12.82036023169082</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-6.530561408243116</v>
+        <v>-4.357142857142925</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-7.068850961338846</v>
+        <v>-4.846391998094745</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-15.46712910561677</v>
+        <v>-12.90693981260918</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-11.20401337792642</v>
+        <v>-8.800929235167921</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-11.67108202171315</v>
+        <v>-9.266761995551263</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-11.73206417823593</v>
+        <v>-9.30373460468806</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-12.58198297456573</v>
+        <v>-10.12756318550311</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-12.78668413282593</v>
+        <v>-10.33170363303913</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-8.404479893514136</v>
+        <v>-10.2735368956743</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1289785729145052</v>
+        <v>-2.335361488904795</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.251069009644496</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.2934</t>
+          <t>X ≈ 0.2928</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>12.17979315831341</v>
+        <v>12.17963976830909</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>17.86557385745736</v>
+        <v>17.86507936507935</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>17.32728430436175</v>
+        <v>17.37583022412752</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>17.62465833399675</v>
+        <v>17.64861574294636</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.42883686361948</v>
+        <v>6.476848542609801</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>5.961768219832742</v>
+        <v>6.011015782226458</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>11.45634161886551</v>
+        <v>11.5295987286452</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.60642282253562</v>
+        <v>10.70577014783019</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.846166108719913</v>
+        <v>4.946074144738589</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.880544261075237</v>
+        <v>5.004240882103481</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.095162147793772</v>
+        <v>-0.9464726000159445</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.869426497567197</v>
+        <v>-0.6974277380005347</v>
       </c>
     </row>
   </sheetData>
@@ -2210,469 +2210,469 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.2106</t>
+          <t>X &gt; -0.2103</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4066</v>
+        <v>4077</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.09062429236323055</v>
+        <v>-0.08957392757646687</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1011298528608648</v>
+        <v>0.1008905959488402</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.01398496601518673</v>
+        <v>0.01395157522367896</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.01415572492187067</v>
+        <v>-0.01410395330141512</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.0498473582130643</v>
+        <v>0.04837060591891884</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1643408736793006</v>
+        <v>0.163235625987312</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.191283326777949</v>
+        <v>0.1894396841921235</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.2779655566587564</v>
+        <v>0.2758537281812323</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.4271104717272181</v>
+        <v>0.4239315720226458</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.3279625440753762</v>
+        <v>0.3243276909160784</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.3091518272966809</v>
+        <v>0.3055512689215902</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1853623535039475</v>
+        <v>0.1814357283348542</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2954342514085226</v>
+        <v>0.2905172098037241</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2646391962623937</v>
+        <v>0.2591579867971063</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.1929</t>
+          <t>X &gt; -0.1926</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4045</v>
+        <v>4055</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.06593328041113722</v>
+        <v>-0.05190140207479033</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.01191562350559394</v>
+        <v>0.02522596578700842</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.04900368586801562</v>
+        <v>-0.03547746402404073</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.05331914158359297</v>
+        <v>-0.03979968371113074</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.03553979255222117</v>
+        <v>-0.04816365163809166</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.102658169509553</v>
+        <v>0.09043486948122137</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1301640545814209</v>
+        <v>0.1170914443002644</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.244387051945516</v>
+        <v>0.2311038831320928</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.3699218657790979</v>
+        <v>0.3555428994169745</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2499562052638993</v>
+        <v>0.2352108967831796</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2567941280435804</v>
+        <v>0.2420601257910988</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1815903034111201</v>
+        <v>0.1662379790278621</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2696975215642041</v>
+        <v>0.2533959075449062</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1881205426745254</v>
+        <v>0.1711844006485919</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.1752</t>
+          <t>X &gt; -0.175</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4009</v>
+        <v>4020</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.01945407131008636</v>
+        <v>-0.0181703421198165</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.09839775205463752</v>
+        <v>0.09817934392541616</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.05901281183580664</v>
+        <v>-0.05884530570062907</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.01477227618561727</v>
+        <v>-0.01471109535626169</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01688913737274333</v>
+        <v>-0.01889137759341253</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.09499274607874497</v>
+        <v>0.09372221983040419</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.148403043345013</v>
+        <v>0.1459708558840802</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2429360626444179</v>
+        <v>0.2401927982887173</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.3452305077544082</v>
+        <v>0.3411929315437661</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2816450170700833</v>
+        <v>0.2766780338474675</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.265463771287763</v>
+        <v>0.2605161034758439</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2640728906771628</v>
+        <v>0.2581223120167309</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2819506258277755</v>
+        <v>0.2748930083181236</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.2225609750638213</v>
+        <v>0.2146783979861979</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.1575</t>
+          <t>X &gt; -0.1573</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3974</v>
+        <v>3985</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1107128702634768</v>
+        <v>-0.1089112245868407</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.04738608513237352</v>
+        <v>0.04731654404773877</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1330466576631295</v>
+        <v>-0.1326725440031922</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.114680493278918</v>
+        <v>-0.1143393527623857</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1121109030476006</v>
+        <v>-0.1142938508739491</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.02322968284434523</v>
+        <v>0.02193571957212725</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1531942277658445</v>
+        <v>0.150306569775239</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.277792787113583</v>
+        <v>0.2744975049915652</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.3564002600651435</v>
+        <v>0.3516538664898263</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2494595243958884</v>
+        <v>0.24366602816783</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1846401120166377</v>
+        <v>0.1789951299163377</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.08231041354560631</v>
+        <v>0.07572319963545482</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1039992777827905</v>
+        <v>0.09606517107179258</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.06721724229747394</v>
+        <v>0.0581835822280965</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.1399</t>
+          <t>X &gt; -0.1397</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3911</v>
+        <v>3922</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1363696492907209</v>
+        <v>-0.1340000078603012</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1266080471894853</v>
+        <v>0.1263348825346924</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1523503059054931</v>
+        <v>-0.151913753175748</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1102826417350116</v>
+        <v>-0.1099404156372685</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.09901955051361</v>
+        <v>-0.1020521354644046</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.05923631590823675</v>
+        <v>0.05743677772160538</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.09056903989988996</v>
+        <v>0.08704056206626376</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1991380890637231</v>
+        <v>0.195220353396401</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2033623883581939</v>
+        <v>0.1977932791927088</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1338813155113954</v>
+        <v>0.126724469446799</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1223825397651623</v>
+        <v>0.115217810697537</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.04339174950411717</v>
+        <v>0.03482192185882838</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.02106143775500868</v>
+        <v>0.01084464585602518</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.005598361093561266</v>
+        <v>0.01932675233885561</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.1222</t>
+          <t>X &gt; -0.122</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3843</v>
+        <v>3850</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2246919641443057</v>
+        <v>-0.1932596374678823</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.00649901075771453</v>
+        <v>-0.02803774484345922</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2315543594170535</v>
+        <v>-0.2264726378032833</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1651093042924998</v>
+        <v>-0.160251665433023</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1701196416404116</v>
+        <v>-0.1690144391416837</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.03759581055406613</v>
+        <v>0.0401830489771271</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.006949572166959683</v>
+        <v>0.01961350098274295</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1637254381578472</v>
+        <v>0.1644274926921128</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1950803576042546</v>
+        <v>0.1936713615894448</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.1133979546732533</v>
+        <v>0.1366644567733246</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.209313967967617</v>
+        <v>0.232575283822122</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1283408222658196</v>
+        <v>0.1236593660079421</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.06104088145820441</v>
+        <v>0.05471035390659296</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.01072236017453321</v>
+        <v>0.00675696618417021</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.1045</t>
+          <t>X &gt; -0.1044</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3743</v>
+        <v>3749</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1633880603691935</v>
+        <v>-0.144348932808299</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1619129416104386</v>
+        <v>-0.1714596093249412</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4090483484385032</v>
+        <v>-0.4178779621873332</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4510231981426287</v>
+        <v>-0.4332269220537412</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5216045845272248</v>
+        <v>-0.5089784802661441</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2364009114316588</v>
+        <v>-0.2749639453392021</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1198409497328257</v>
+        <v>-0.134795049864465</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.01189960331466722</v>
+        <v>-0.02685964313232603</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.0047724583724289</v>
+        <v>-0.02252345213972973</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1480338594737916</v>
+        <v>0.1009206940599157</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1720208095746116</v>
+        <v>0.1249417116658549</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1947604275489496</v>
+        <v>0.1447959933330765</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.1486410997498311</v>
+        <v>0.1379718444285416</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.02637131307466234</v>
+        <v>0.002018040132888643</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.0868</t>
+          <t>X &gt; -0.08673</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3621</v>
+        <v>3628</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1261928137896504</v>
+        <v>-0.1069258869578391</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.04012928136049254</v>
+        <v>0.02759021083627999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2570581322165424</v>
+        <v>-0.2688350874204772</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2497023890206478</v>
+        <v>-0.2614859027723284</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.524935160761018</v>
+        <v>-0.5433950225654982</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2677238440997129</v>
+        <v>-0.2831774363715667</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1719294199054247</v>
+        <v>-0.1913464749662381</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1824554740598288</v>
+        <v>-0.2019115094019952</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1454616749057607</v>
+        <v>-0.1687222182306485</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.06896653687395826</v>
+        <v>0.04130612433537095</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1559332080479052</v>
+        <v>0.1279952561556996</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1626946799282223</v>
+        <v>0.1465732971631653</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1844107142149198</v>
+        <v>0.1802534647096152</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.07874619874137068</v>
+        <v>0.1141611386379608</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.06912</t>
+          <t>X &gt; -0.06908</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3472</v>
+        <v>3478</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1970895438925808</v>
+        <v>-0.2002122553030574</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.06911361785105186</v>
+        <v>-0.04621657938841395</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3908689093305142</v>
+        <v>-0.3670154140049675</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.302594310710802</v>
+        <v>-0.3077459588085745</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.7965772621228453</v>
+        <v>-0.7814681256443379</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1671841413900239</v>
+        <v>-0.1926814577303162</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.1368197020370943</v>
+        <v>-0.151503947811662</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.07020620063089211</v>
+        <v>-0.1000953288846489</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.08616315024145393</v>
+        <v>0.06408148726590213</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3175275350800533</v>
+        <v>0.3034712972555198</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2154697441525855</v>
+        <v>0.2142733784550543</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3074515831438518</v>
+        <v>0.3299113801877738</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.3769320662359661</v>
+        <v>0.4108778519019509</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.257045596646833</v>
+        <v>0.3312605247302827</v>
       </c>
     </row>
     <row r="15">
@@ -2685,1086 +2685,1086 @@
         <v>3271</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.02519643890329348</v>
+        <v>0.05399073921558539</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.553374649017961</v>
+        <v>0.5937339907205228</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.144737619742159</v>
+        <v>0.1556120753748971</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1526760008725674</v>
+        <v>0.1494260398934983</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2021834085361789</v>
+        <v>-0.1703528782903803</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.4009075272438096</v>
+        <v>0.4080561124111881</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5607706928935627</v>
+        <v>0.5918988006918369</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.7357075520111493</v>
+        <v>0.7678753312620472</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7970121579463267</v>
+        <v>0.8531521108782982</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.139389295581616</v>
+        <v>1.221255070405626</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.9958315185504034</v>
+        <v>1.078239317246059</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.060781361520228</v>
+        <v>1.166968401799217</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.129777558038668</v>
+        <v>1.26080803024761</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.172083064578253</v>
+        <v>1.344081824144915</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.03374</t>
+          <t>X &gt; -0.03378</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2987</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1136604676243351</v>
+        <v>0.1320286433404405</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8124844180824269</v>
+        <v>0.8414718795188918</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.551626659038817</v>
+        <v>0.5665206250694936</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.6483733961993181</v>
+        <v>0.6478789038213151</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1770406559593383</v>
+        <v>0.2255865757251101</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4074578727387106</v>
+        <v>0.4314152816883237</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.8584020163182089</v>
+        <v>0.9064136953085296</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.261771939655681</v>
+        <v>1.311019502049398</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.334703408844312</v>
+        <v>1.407960518624009</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.589572024633632</v>
+        <v>1.688919349928206</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.518784492084862</v>
+        <v>1.618692528103537</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.385770612300917</v>
+        <v>1.509467233329161</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.43431744897746</v>
+        <v>1.583006996755287</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.425704254209016</v>
+        <v>1.597703013775678</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.01606</t>
+          <t>X &gt; -0.01612</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2665</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3896280595219324</v>
+        <v>0.4134264059975763</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.367560165332399</v>
+        <v>1.399774457036273</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.8977418762621667</v>
+        <v>0.9143234392268553</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.140537376323323</v>
+        <v>1.14004288394532</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2645367538092458</v>
+        <v>0.3130826735750176</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.4868638791291247</v>
+        <v>0.5108212880787377</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.002528754384535</v>
+        <v>1.050540433374856</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.28592915374977</v>
+        <v>1.335176716143486</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.487611162330182</v>
+        <v>1.560868272109879</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.913489739358674</v>
+        <v>2.012837064653247</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.783835485413675</v>
+        <v>1.883743521432351</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.593072924823417</v>
+        <v>1.716769545851662</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.585680045243585</v>
+        <v>1.734369593021412</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.886462599785311</v>
+        <v>2.058461359351973</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.00163</t>
+          <t>X &gt; 0.001527</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2285</v>
+        <v>2288</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.085823575592556</v>
+        <v>1.070674201313892</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.706584966117354</v>
+        <v>1.695265043648732</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.880741371296665</v>
+        <v>1.850385689055045</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.923439162587435</v>
+        <v>1.892857142857139</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.385149609491741</v>
+        <v>1.447314295611513</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.857578343722018</v>
+        <v>1.894924989255614</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.735668859729373</v>
+        <v>2.795807361568613</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.88129168202579</v>
+        <v>2.941862713073384</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.082891582395781</v>
+        <v>3.167127866174347</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.370828365934642</v>
+        <v>3.479662921723005</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.209890883823235</v>
+        <v>3.3192287678932</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.112978007732174</v>
+        <v>3.24627662413922</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.867881859013956</v>
+        <v>3.025943872400575</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.831035452347706</v>
+        <v>3.012750972178182</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.01932</t>
+          <t>X &gt; 0.01918</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.937688620628442</v>
+        <v>1.932036935443591</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.807122682603371</v>
+        <v>2.828198693262948</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.825787990354783</v>
+        <v>2.847683845444109</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.800974374253229</v>
+        <v>2.82260920897285</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.211005234594232</v>
+        <v>2.281707175458934</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.456699677666009</v>
+        <v>2.502839801715879</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.198862703412757</v>
+        <v>3.268629993482151</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.3002695118224</v>
+        <v>3.370979051280635</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.394326114989553</v>
+        <v>3.488965119829778</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.146474502122224</v>
+        <v>4.266376208436292</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.838414170735412</v>
+        <v>3.958929975776243</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.666073976837502</v>
+        <v>3.810485142893192</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.607680229467249</v>
+        <v>3.77689746426325</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.419979187187323</v>
+        <v>3.612719185782751</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.037</t>
+          <t>X &gt; 0.03683</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.727004761544862</v>
+        <v>1.664285206652906</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.838590945708745</v>
+        <v>2.864039475856984</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.567581937191328</v>
+        <v>2.532144406528047</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.388401140185636</v>
+        <v>2.352813852813853</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.97387396332757</v>
+        <v>1.987250549833483</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.961842052368588</v>
+        <v>1.950821473723529</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.929111891122226</v>
+        <v>2.941495007256265</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.018973940404791</v>
+        <v>3.032248517744911</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.329278912594887</v>
+        <v>3.366333422522764</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.212033383591759</v>
+        <v>4.27410657330951</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.883569849093945</v>
+        <v>3.946280287801876</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.04171037768689</v>
+        <v>4.128132863138312</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.930965464967549</v>
+        <v>4.042189531503375</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.723532798362392</v>
+        <v>3.85833396061831</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.05469</t>
+          <t>X &gt; 0.05448</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.003388902201074</v>
+        <v>2.008185411856857</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.335401613322603</v>
+        <v>2.292073300562087</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.641676566385193</v>
+        <v>1.59960491642962</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.323471216700014</v>
+        <v>1.281393363917637</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.009396910241087</v>
+        <v>1.016192019829042</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.306770939876174</v>
+        <v>1.363660137602416</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.044183151611506</v>
+        <v>2.124512636875828</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.473975494371849</v>
+        <v>2.480188464991372</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.637208584485847</v>
+        <v>2.741946251672346</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.730488592341338</v>
+        <v>3.8598652436729</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.226833771898782</v>
+        <v>3.356994400319039</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.709642417527647</v>
+        <v>3.863256731410594</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.111614135215731</v>
+        <v>4.289607393345641</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.963657707714319</v>
+        <v>4.165239260588791</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.07238</t>
+          <t>X &gt; 0.07214</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.703935186778537</v>
+        <v>2.665405726868187</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.256860906158359</v>
+        <v>3.332453664214583</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.50140421932938</v>
+        <v>2.578679672299529</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.180772735325313</v>
+        <v>2.258518709013757</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.093339809822048</v>
+        <v>2.21931457256229</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.112084443605013</v>
+        <v>3.212172098581931</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.199601316079153</v>
+        <v>4.231624020157554</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4.363731950921803</v>
+        <v>4.395854266074842</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.212578468880544</v>
+        <v>4.178863655137867</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.985743531883422</v>
+        <v>5.065206091424585</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.781042373623229</v>
+        <v>4.861065643888494</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>5.356448479089458</v>
+        <v>5.459286386653936</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5.838010880960908</v>
+        <v>5.964218469091009</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5.612889903595004</v>
+        <v>5.763218326605923</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.09006</t>
+          <t>X &gt; 0.08979</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.878199991565097</v>
+        <v>2.886363946038131</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.139942075296844</v>
+        <v>4.056490825639976</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.634673452972741</v>
+        <v>3.552620678734968</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.538379259544534</v>
+        <v>4.453429830081809</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.447603518603536</v>
+        <v>3.41351989617835</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.855474785807687</v>
+        <v>3.796437573587582</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.64921746521555</v>
+        <v>5.608028180397362</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.182148821428811</v>
+        <v>5.142195420014019</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.784150090320402</v>
+        <v>5.76601576241908</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>6.26019814481927</v>
+        <v>6.263773084687791</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>6.055496986559078</v>
+        <v>6.059632637151701</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.752858564328754</v>
+        <v>6.778592326058444</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7.106188373998776</v>
+        <v>7.154359509626772</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>7.000432311518132</v>
+        <v>7.073007895871221</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.1077</t>
+          <t>X &gt; 0.1074</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.428778524578526</v>
+        <v>3.38392791021235</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.60643705302865</v>
+        <v>4.582207778698887</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.805291166281577</v>
+        <v>5.777873763894114</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.333922684371927</v>
+        <v>6.30510879848628</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.13162250710625</v>
+        <v>5.28605833303105</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.163392287073343</v>
+        <v>5.293943189598323</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>7.070713800317129</v>
+        <v>7.22004206726028</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.736447281364391</v>
+        <v>6.886659638002762</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.94106937450961</v>
+        <v>7.114587691117613</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.419171826519722</v>
+        <v>7.615262421560921</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>7.21447066825953</v>
+        <v>7.41112197402483</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>8.178463694452837</v>
+        <v>8.396441029270513</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>9.351938339147395</v>
+        <v>9.590687076216618</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>9.179267614871925</v>
+        <v>9.442380944854499</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.1254</t>
+          <t>X &gt; 0.1251</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.415635693603583</v>
+        <v>4.588172106470267</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.371847719662007</v>
+        <v>4.409051183560905</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.014693889765908</v>
+        <v>6.043394318491131</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7.242097716739849</v>
+        <v>7.265322041453082</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>5.763369292170793</v>
+        <v>5.684029218753892</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>5.904003509893663</v>
+        <v>5.800808497323217</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.916471834013073</v>
+        <v>6.98820233009463</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.389842061699682</v>
+        <v>7.458407011208948</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.015380281352456</v>
+        <v>7.109421921572924</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.419379980320407</v>
+        <v>7.533643262754829</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.371418633972432</v>
+        <v>7.485509055468341</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.659715281625573</v>
+        <v>8.791725714830129</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>9.963702359346641</v>
+        <v>10.112636431012</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>9.405738950012044</v>
+        <v>9.581650091779331</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.1431</t>
+          <t>X &gt; 0.1427</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>534</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.324327415158535</v>
+        <v>3.295131620805904</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.147598250933655</v>
+        <v>4.146411464488999</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.561815630223563</v>
+        <v>6.561662240219242</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>8.190168114635888</v>
+        <v>8.189673622257885</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.153751220716231</v>
+        <v>6.202297140482003</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>7.012923003160296</v>
+        <v>7.036880412109909</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.051808149512112</v>
+        <v>8.099819828502433</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.521069093740351</v>
+        <v>8.570316656134068</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8.085555102011583</v>
+        <v>8.158812211791279</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.171965893696708</v>
+        <v>8.271313218991281</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.843669229818538</v>
+        <v>6.943577265837213</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.750706558203824</v>
+        <v>8.874403179232068</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>8.8923534576994</v>
+        <v>9.041043005477228</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.181759519910962</v>
+        <v>8.353758279477624</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.1608</t>
+          <t>X &gt; 0.1604</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.840923049925415</v>
+        <v>3.754125077163131</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.758472589045496</v>
+        <v>5.132223618430963</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>7.352206951416896</v>
+        <v>7.471970823738133</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.861742439832845</v>
+        <v>8.96859746176375</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.403912656852086</v>
+        <v>7.568186589604544</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.011631514073386</v>
+        <v>6.929810377216178</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.306231499634798</v>
+        <v>8.235896884801654</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.218473200675653</v>
+        <v>9.364597154031067</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.697720929210348</v>
+        <v>8.87204367929062</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>8.537457305294282</v>
+        <v>8.731586396881113</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.413215917149024</v>
+        <v>7.616284218137729</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>8.826904414331942</v>
+        <v>9.041193552313551</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.096408733432327</v>
+        <v>9.329406924155187</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.712948981359993</v>
+        <v>7.983918756557806</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.1785</t>
+          <t>X &gt; 0.1781</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.074639525021205</v>
+        <v>2.985866727391837</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.818466982092872</v>
+        <v>2.743172215962531</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.133722697608839</v>
+        <v>5.030399375100899</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.786983071549507</v>
+        <v>8.645538108004587</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.89367996831831</v>
+        <v>6.815806393326127</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.378045867872096</v>
+        <v>6.552398882654437</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7.648349058741424</v>
+        <v>7.832225367155523</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>9.078299385144398</v>
+        <v>9.243068209989339</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.933306388513216</v>
+        <v>8.133709541871305</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.896395722264657</v>
+        <v>8.11417050529225</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.878686433923164</v>
+        <v>7.105740513520232</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.997075426386893</v>
+        <v>8.236293309866362</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.660935413181875</v>
+        <v>8.913521442283773</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.718649383191611</v>
+        <v>7.017794186336666</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.1962</t>
+          <t>X &gt; 0.1957</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.9646285239211</v>
+        <v>2.899724240686787</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.343541440758251</v>
+        <v>2.628022565367004</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.259001079105524</v>
+        <v>4.529366544265407</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.01958925899752</v>
+        <v>8.265807962529266</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.491200696000831</v>
+        <v>6.792952264200302</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.798475715734931</v>
+        <v>6.082131225642179</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.70386436636975</v>
+        <v>7.00508169379377</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.886960739084664</v>
+        <v>8.17859319570551</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.495945579261559</v>
+        <v>7.813751734109701</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>6.976059786232028</v>
+        <v>7.317792005753731</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.111292621371177</v>
+        <v>6.457913853299601</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.47570377702683</v>
+        <v>6.84394944312352</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.035750943515396</v>
+        <v>8.41600463131379</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.611321577240282</v>
+        <v>7.025705231034074</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.2139</t>
+          <t>X &gt; 0.2134</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.365237815619494</v>
+        <v>0.4310646457012552</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1814021499060914</v>
+        <v>-0.7319443722277086</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.205434183954466</v>
+        <v>2.235662177272708</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.754462746346256</v>
+        <v>6.567226890756295</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.224720201797574</v>
+        <v>3.977137413669929</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.094743804082221</v>
+        <v>2.989418730808175</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.292084726867344</v>
+        <v>4.189266843263397</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.397665655730179</v>
+        <v>3.723434082880054</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.336683499207403</v>
+        <v>4.106629540970147</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.341465557578395</v>
+        <v>3.702969027382053</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.846166108719913</v>
+        <v>4.759332781526631</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.880544261075237</v>
+        <v>5.23766758611842</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.597145544513957</v>
+        <v>6.94334999568904</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>5.540829912689212</v>
+        <v>5.931890656023739</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.2316</t>
+          <t>X &gt; 0.231</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1506629168340652</v>
+        <v>0.6148881751130162</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.513154755177126</v>
+        <v>-2.009955576709501</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2763471925637475</v>
+        <v>0.2004731016424586</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.538088477340409</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1580958125973879</v>
+        <v>0.361941335238555</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.439669151383363</v>
+        <v>-0.9277731459425169</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.107199436718886</v>
+        <v>1.615737431498687</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.6401307929321476</v>
+        <v>1.149904671115344</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.05283284693570067</v>
+        <v>0.5920987286452117</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.834492997974259</v>
+        <v>2.372436814496901</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.103476050240381</v>
+        <v>1.647463033627474</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.6115384131220125</v>
+        <v>1.184796437659031</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.770334928229666</v>
+        <v>2.352138511095205</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.996070578456198</v>
+        <v>2.601183373110572</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.2492</t>
+          <t>X &gt; 0.2487</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.8974623478440265</v>
+        <v>0.5100224033009368</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.428859379841491</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.784170805650525</v>
+        <v>-1.466892670169621</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.075784067667577</v>
+        <v>3.360977948226271</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.516559539482174</v>
+        <v>-1.155116830309545</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-3.921888212549788</v>
+        <v>-3.566895069879877</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.330922896140287</v>
+        <v>-2.956410219508022</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-3.797991539927025</v>
+        <v>-3.422242979891365</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.183298020774117</v>
+        <v>-2.788074649430847</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.006189790076952</v>
+        <v>-1.598480411453885</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.210890948337145</v>
+        <v>-1.802620858989975</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-3.527864147333183</v>
+        <v>-3.086736000819712</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.59666364929523</v>
+        <v>-2.139612048188908</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.046603674744375</v>
+        <v>-3.232849065368171</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.2669</t>
+          <t>X &gt; 0.2663</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.519083969465655</v>
+        <v>3.839094524319364</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.49210212359818</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.48687350835322</v>
+        <v>-2.106074517405155</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.443351635235139</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.69493791786055</v>
+        <v>-3.259090410793185</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-6.597563888225466</v>
+        <v>-6.160908066577441</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-3.482274247491631</v>
+        <v>-3.046960981199717</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-3.94934289127837</v>
+        <v>-3.51279374158306</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.210325047801149</v>
+        <v>-2.756115557069066</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.260243844131004</v>
+        <v>-2.786293344233258</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.864945002391195</v>
+        <v>-1.403132204467759</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-2.630566850035876</v>
+        <v>-2.932267054404456</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-3.050717703349285</v>
+        <v>-3.327424980968281</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-5.224982053122751</v>
+        <v>-5.459332499905301</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.2846</t>
+          <t>X &gt; 0.284</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>102</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.440652596916628</v>
+        <v>1.411456802563997</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.4150872759605093</v>
+        <v>0.414933885956188</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.466881046999852</v>
+        <v>4.466386554621849</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.934153604135055</v>
+        <v>-2.885607684369283</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.741097776903395</v>
+        <v>-1.693086097913074</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-2.208166420690134</v>
+        <v>-2.158918858296417</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.288756420350168</v>
+        <v>-1.215499310570472</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.158283059817279</v>
+        <v>-1.058935734522706</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.5978000956480116</v>
+        <v>0.6977081316666869</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.328606065722148</v>
+        <v>-1.204909444693904</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-3.709541232761048</v>
+        <v>-3.56085168498322</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-5.444589896260013</v>
+        <v>-5.27259113669335</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.3023</t>
+          <t>X &gt; 0.3016</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.280988731370414</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-2.105921127400833</v>
+        <v>-2.106074517405155</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.595732587616098</v>
+        <v>1.595238095238095</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.275890298812939</v>
+        <v>-7.227344379047167</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-9.359468650130225</v>
+        <v>-9.335511241180612</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-3.491798057015444</v>
+        <v>-3.443786378025123</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-3.958866700802183</v>
+        <v>-3.909619138408466</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-4.019848857324959</v>
+        <v>-3.946591747545263</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-3.679291463178622</v>
+        <v>-3.579944137884048</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3125640500102449</v>
+        <v>-0.2126560139915696</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-2.659138278607308</v>
+        <v>-2.535441657579064</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-4.2697653223969</v>
+        <v>-4.121075774619072</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
   </sheetData>
@@ -3904,469 +3904,469 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.2106</t>
+          <t>X &lt; -0.2103</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.852417302798983</v>
+        <v>5.823221508446352</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.711149742645794</v>
+        <v>-1.71233652909045</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2750312535515462</v>
+        <v>0.2748778635472249</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1330331559557862</v>
+        <v>-0.08448723619001441</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.407087697749276</v>
+        <v>-3.383130288799663</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.301321866539247</v>
+        <v>-2.253310187548927</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-6.339819081754563</v>
+        <v>-6.290571519360846</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-11.16270600018211</v>
+        <v>-11.08944889040241</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-7.250720034607198</v>
+        <v>-7.151372709312625</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.455421192867391</v>
+        <v>-7.355513156848716</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2781858976549216</v>
+        <v>-0.154489276626677</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-5.460241512873097</v>
+        <v>-5.311551965095269</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.044029672170367</v>
+        <v>-3.872030912603705</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.1929</t>
+          <t>X &lt; -0.1926</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.709560159941837</v>
+        <v>3.15026553360358</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.098374066878009</v>
+        <v>1.567088448447727</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.116746686548119</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.738589730473244</v>
+        <v>3.190026954177895</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.200300177377549</v>
+        <v>3.644174039641065</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.311849602511181</v>
+        <v>0.1433746527996149</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5558209906036069</v>
+        <v>1.026114789989251</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.720771462706949</v>
+        <v>-3.21330287605447</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-6.63889647637258</v>
+        <v>-6.080464164436549</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.726910510797673</v>
+        <v>-2.187311613176057</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-3.883992621438814</v>
+        <v>-3.334848287127244</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.04009065955968794</v>
+        <v>0.4969033558980271</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-3.317384370015951</v>
+        <v>-2.728443249911081</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.2345058626465644</v>
+        <v>0.3507902913495684</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.1752</t>
+          <t>X &lt; -0.175</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>141</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.419793189323805</v>
+        <v>1.390597394971174</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.9006127618960562</v>
+        <v>-0.901799548340712</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.250715144129053</v>
+        <v>2.250561754124732</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.671720429561383</v>
+        <v>1.67122593718338</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.842650734621721</v>
+        <v>1.891196654387493</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.01236518978871715</v>
+        <v>0.03632259873833021</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.07234516947745107</v>
+        <v>-0.0243334904871304</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-2.667073387732273</v>
+        <v>-2.617825825338556</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.146495260567107</v>
+        <v>-4.073238150787411</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.868754482428884</v>
+        <v>-2.76940715713431</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.073455640689076</v>
+        <v>-2.973547604670401</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.32985763017772</v>
+        <v>-2.206161009149476</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.750008483491129</v>
+        <v>-2.601318935713302</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.105833116952539</v>
+        <v>-0.9338343573858765</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.1575</t>
+          <t>X &lt; -0.1573</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>176</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.200902151283827</v>
+        <v>3.171706356931196</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.4533524218563585</v>
+        <v>0.4521656354117027</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.46767194619224</v>
+        <v>3.467518556187919</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.597897089780602</v>
+        <v>3.597402597402599</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.627789354866721</v>
+        <v>3.676335274632493</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.652436111774534</v>
+        <v>1.676393520724147</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1368197020370943</v>
+        <v>-0.0888080230467736</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.876615618551099</v>
+        <v>-2.827368056157383</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.505779593255689</v>
+        <v>-3.432522483475992</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.514789298676469</v>
+        <v>-1.415441973381895</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5831268205730211</v>
+        <v>-0.4832187845543459</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.292160422691396</v>
+        <v>2.41585704371964</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.872009569377987</v>
+        <v>2.020699117155814</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.665927037786339</v>
+        <v>2.837925797353002</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.1399</t>
+          <t>X &lt; -0.1397</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>239</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.749209492478201</v>
+        <v>2.72001369812557</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.9540268097906477</v>
+        <v>-0.9552135962353034</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.835302223864353</v>
+        <v>2.835148833860032</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.547117325611715</v>
+        <v>2.546622833233712</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.427237814357021</v>
+        <v>2.475783734122793</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.6325616347870877</v>
+        <v>0.6565190437367008</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.9662613173619192</v>
+        <v>1.01427299635224</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.756037451947833</v>
+        <v>-0.7067898895541163</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.01980047521140449</v>
+        <v>0.09305758499110084</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.8435218462455651</v>
+        <v>0.9428691715401385</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.6388206879853726</v>
+        <v>0.7387287240040479</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.346839007704709</v>
+        <v>2.470535628732954</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.763508238073307</v>
+        <v>2.912197785851134</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.989243888299839</v>
+        <v>2.742832606025502</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.1222</t>
+          <t>X &lt; -0.122</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.219409702364672</v>
+        <v>2.795354413055144</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.956757811255244</v>
+        <v>1.21217732789929</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.167849618682617</v>
+        <v>3.069243198105482</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.646608964225372</v>
+        <v>2.556040422599899</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.759785209175284</v>
+        <v>2.709878098368243</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.7770289456507555</v>
+        <v>0.7318597586662747</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.995250182475793</v>
+        <v>1.635833894521198</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1004829564249476</v>
+        <v>-0.1161724993026709</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1642677860750723</v>
+        <v>0.1683982999206748</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.9430134848592218</v>
+        <v>0.6307433525462045</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.5646192694921766</v>
+        <v>-0.8595707284303984</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.7726904789543525</v>
+        <v>0.8063130507351275</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.655471221732149</v>
+        <v>1.697328757611814</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.532672670004288</v>
+        <v>2.267917027987323</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.1045</t>
+          <t>X &lt; -0.1044</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.797812575822611</v>
+        <v>1.616101767346024</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.142616702807693</v>
+        <v>2.217390701607648</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.94833431560766</v>
+        <v>4.008118732710415</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.567557014208248</v>
+        <v>4.380721220527036</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.251761348643115</v>
+        <v>5.10506431258483</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.104147603217079</v>
+        <v>3.436102258588221</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.530439688938678</v>
+        <v>2.647290829556937</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.574373490139713</v>
+        <v>1.696021175969712</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.002388888629163</v>
+        <v>2.144485460036798</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4189737597809682</v>
+        <v>0.8352199860179326</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.03022617598532662</v>
+        <v>0.3883610918799008</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.004151976369996646</v>
+        <v>0.4465278292447934</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4571254339056097</v>
+        <v>0.5368067958848499</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.051676423535717</v>
+        <v>1.756725444307982</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.0868</t>
+          <t>X &lt; -0.08673</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>0.9608074996908726</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2312061470785167</v>
+        <v>0.3157167184749881</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.904103935255804</v>
+        <v>1.985768598828201</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.034329078844166</v>
+        <v>2.115652640042882</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.939648548304866</v>
+        <v>4.065427889334856</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>2.649658061061864</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.272612970553482</v>
+        <v>2.401384711048401</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.369454101202827</v>
+        <v>2.498403733029043</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.496441869492081</v>
+        <v>2.649048384680235</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.8946433739141071</v>
+        <v>1.074750760713279</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1260324412178235</v>
+        <v>0.3077585308132171</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2666082912070635</v>
+        <v>0.3659252681781098</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1417351268393929</v>
+        <v>0.1583846024022719</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8529007446088173</v>
+        <v>0.5950467252056413</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.06912</t>
+          <t>X &lt; -0.06908</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.184773119025763</v>
+        <v>1.190904140279926</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.7466075538211712</v>
+        <v>0.6236922220326306</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.111366960854994</v>
+        <v>1.971608805561182</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.801709406496137</v>
+        <v>1.811217084801982</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.342598739030947</v>
+        <v>4.224725563588812</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.414166317053123</v>
+        <v>1.531044683514843</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.558548072625847</v>
+        <v>1.615737431498687</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.238322306959518</v>
+        <v>1.377342807942128</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.7368115160755053</v>
+        <v>0.8396084468181968</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.5536359146155903</v>
+        <v>-0.4864439640919116</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.1709655603941371</v>
+        <v>-0.1708849195888931</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.4952727323888197</v>
+        <v>-0.6163870664893309</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.833339205558417</v>
+        <v>-1.011544993053157</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2302917876360269</v>
+        <v>-0.6160872467039695</v>
       </c>
     </row>
     <row r="15">
@@ -4376,1089 +4376,1089 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.04433649471818057</v>
+        <v>-0.06022318346159494</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.732551561800427</v>
+        <v>-1.866117417837934</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4419296881284964</v>
+        <v>-0.4781182123887291</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.3633975211203122</v>
+        <v>-0.3482341711740489</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9609179379952977</v>
+        <v>0.8328953070277123</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.046267383152191</v>
+        <v>-1.061900793657124</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.409136549974711</v>
+        <v>-1.509262568501313</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.041998258510013</v>
+        <v>-2.139201474136051</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.042904233321508</v>
+        <v>-2.228790533099755</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.39886219067688</v>
+        <v>-3.665263820068233</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.976963142980772</v>
+        <v>-3.250238760094504</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.109113955597742</v>
+        <v>-3.469384258188327</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.35526315789474</v>
+        <v>-3.80539894208831</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.52395816233777</v>
+        <v>-4.118151832881935</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.03374</t>
+          <t>X &lt; -0.03378</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1163</v>
+        <v>1174</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1849976631874171</v>
+        <v>-0.2297064194815803</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.836782974662007</v>
+        <v>-1.897342964096893</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.335255109716087</v>
+        <v>-1.362026898357541</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.50072338607773</v>
+        <v>-1.48552123552124</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.287429385437342</v>
+        <v>-0.4085221756095763</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.711995997533748</v>
+        <v>-0.7664998802910858</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.690821256038639</v>
+        <v>-1.79768339830656</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.711361710782221</v>
+        <v>-2.811959735664317</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.727448335472388</v>
+        <v>-2.889400423178365</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.446704855270674</v>
+        <v>-3.668876145322002</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.348993029835462</v>
+        <v>-3.573703066627409</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.925845819992958</v>
+        <v>-3.215713766422603</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.042470280668873</v>
+        <v>-3.395645176848063</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.028593403079761</v>
+        <v>-3.442080397474321</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.01606</t>
+          <t>X &lt; -0.01612</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1485</v>
+        <v>1496</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.6117571520296821</v>
+        <v>-0.6508820772110226</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.255094775568786</v>
+        <v>-2.300460224783876</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.545697037764981</v>
+        <v>-1.565380152009602</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.91517679285851</v>
+        <v>-1.900303547713911</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3433984265620253</v>
+        <v>-0.4277873469319857</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.6122993202415401</v>
+        <v>-0.6507341388503178</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.398091941861608</v>
+        <v>-1.473916593784089</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.896492455329344</v>
+        <v>-1.970934210376008</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.123076725653497</v>
+        <v>-2.238999983324582</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.937342568106828</v>
+        <v>-3.094229852169775</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.770321346477225</v>
+        <v>-2.929546639487931</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.363720851380869</v>
+        <v>-2.568819494695219</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.343853638746332</v>
+        <v>-2.594212524308936</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.889628517769218</v>
+        <v>-3.178116983395661</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.00163</t>
+          <t>X &lt; 0.001527</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1865</v>
+        <v>1873</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.256208895284082</v>
+        <v>-1.236226474568511</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.934403668616831</v>
+        <v>-1.917068103248774</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.248067538203969</v>
+        <v>-2.204648979036939</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.249981698098189</v>
+        <v>-2.206319702602237</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.58650675457347</v>
+        <v>-1.658294229763214</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.061525447221726</v>
+        <v>-2.101517165081269</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.026291341508724</v>
+        <v>-3.091709377011952</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.19851445728586</v>
+        <v>-3.26401230600014</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.338667293790458</v>
+        <v>-3.433127575934122</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.732796011065197</v>
+        <v>-3.856474568916347</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.588285473483282</v>
+        <v>-3.713011380018578</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.418568992510437</v>
+        <v>-3.573536895674302</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.113740211387871</v>
+        <v>-3.30032057819686</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.073775618806401</v>
+        <v>-3.289822588804363</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.01932</t>
+          <t>X &lt; 0.01918</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2215</v>
+        <v>2225</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.628133265722866</v>
+        <v>-1.616456775735955</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.318415549731995</v>
+        <v>-2.327531198822456</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.420386536205868</v>
+        <v>-2.42978181785665</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.356648364764858</v>
+        <v>-2.366091403004155</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.837383961026013</v>
+        <v>-1.89205001062836</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.965984940857048</v>
+        <v>-1.998595283575</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.522058225889474</v>
+        <v>-2.573330668859739</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.605443746748882</v>
+        <v>-2.657244589305996</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.597712435188541</v>
+        <v>-2.670700225016972</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.288725142012936</v>
+        <v>-3.381264396808618</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.063862946484974</v>
+        <v>-3.157855637826742</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.870169917243814</v>
+        <v>-2.98607992815446</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.814977631147123</v>
+        <v>-2.953061399057532</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.655230360120498</v>
+        <v>-2.814781046365077</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.037</t>
+          <t>X &lt; 0.03683</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2534</v>
+        <v>2544</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.04785753033805</v>
+        <v>-1.004441117026211</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.696186962561256</v>
+        <v>-1.706747438994327</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.598857791260876</v>
+        <v>-1.571175626341883</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.447843333318318</v>
+        <v>-1.420572771003471</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.178854551757524</v>
+        <v>-1.184033987910681</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.096383715133413</v>
+        <v>-1.086145664228837</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.632293924784044</v>
+        <v>-1.63543857790939</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.684775962144514</v>
+        <v>-1.688330623002308</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.803471956032737</v>
+        <v>-1.822042437825296</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.395941243658193</v>
+        <v>-2.428714415225762</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.224740035895337</v>
+        <v>-2.258480232960665</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.287349184420741</v>
+        <v>-2.336249647703625</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.212847880864082</v>
+        <v>-2.278059589756133</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.084019148623945</v>
+        <v>-2.164932979090686</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.05469</t>
+          <t>X &lt; 0.05448</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2812</v>
+        <v>2822</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.9056947915963036</v>
+        <v>-0.9051735532820473</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.011365579688835</v>
+        <v>-0.9881371810378994</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.749714457697884</v>
+        <v>-0.7277611023815425</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5650112279824384</v>
+        <v>-0.5435835351089651</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4107124658931696</v>
+        <v>-0.413329476017779</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.4840887109205028</v>
+        <v>-0.5100022389931738</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7624445206381409</v>
+        <v>-0.7989850852917044</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.9619759643798673</v>
+        <v>-0.9628958946555244</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.9682235213545738</v>
+        <v>-1.016091638056821</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.514789298676469</v>
+        <v>-1.573069201072812</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.309349975748212</v>
+        <v>-1.368576789381379</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.504198690831906</v>
+        <v>-1.574292325324912</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.691599324394431</v>
+        <v>-1.773016465879643</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.624128568058737</v>
+        <v>-1.71719307385375</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.07238</t>
+          <t>X &lt; 0.07214</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3041</v>
+        <v>3050</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9419507391132598</v>
+        <v>-0.926696872226195</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.095050043676792</v>
+        <v>-1.12137512820091</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8826795371867746</v>
+        <v>-0.9097645657864888</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7348850084882272</v>
+        <v>-0.7623716153127944</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.698216606385138</v>
+        <v>-0.7437440739365613</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.006222464807948</v>
+        <v>-1.041886400793182</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.335817554578242</v>
+        <v>-1.346725767716229</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.391548339259991</v>
+        <v>-1.402451349827061</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.270732139068379</v>
+        <v>-1.258180867645017</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.577485223441357</v>
+        <v>-1.605952183538463</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.534327393981222</v>
+        <v>-1.563006176985034</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.711999646618203</v>
+        <v>-1.749072063870017</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.884116782902211</v>
+        <v>-1.929756769140774</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.804791326388127</v>
+        <v>-1.859540670605277</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.09006</t>
+          <t>X &lt; 0.08979</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3245</v>
+        <v>3253</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7620701127934097</v>
+        <v>-0.764857691390354</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.067846673797753</v>
+        <v>-1.045815709430279</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9856450071247167</v>
+        <v>-0.963742584632044</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.207646828666554</v>
+        <v>-1.185215183223157</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.8998549430603049</v>
+        <v>-0.8917629361695845</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9547726186281764</v>
+        <v>-0.9397518334616777</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.3919913446626</v>
+        <v>-1.382728826170023</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.258232463717619</v>
+        <v>-1.249220827503862</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.364171201647302</v>
+        <v>-1.361745654411884</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.520385426156246</v>
+        <v>-1.524298422428693</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.492777514706468</v>
+        <v>-1.496732298067855</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.657114432419611</v>
+        <v>-1.667546112264162</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.752381289301233</v>
+        <v>-1.769391400808097</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.72544430273755</v>
+        <v>-1.749448095277586</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.1077</t>
+          <t>X &lt; 0.1074</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3397</v>
+        <v>3406</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7213852387454978</v>
+        <v>-0.7113402542522991</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.9386846991335247</v>
+        <v>-0.9335463705460612</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.259173977836781</v>
+        <v>-1.253196052586397</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.348136477473979</v>
+        <v>-1.341920374707264</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.078144024730783</v>
+        <v>-1.112863447582335</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.029281949899477</v>
+        <v>-1.058667990699405</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.392027478983991</v>
+        <v>-1.425941443391444</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.314491289750308</v>
+        <v>-1.348629912706464</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.300860027225021</v>
+        <v>-1.34052733409299</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.429252959097191</v>
+        <v>-1.474092999774847</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.412003825920607</v>
+        <v>-1.456911416357862</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.596851051271543</v>
+        <v>-1.646776332294017</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.853778327245692</v>
+        <v>-1.908544152049295</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.817975871197518</v>
+        <v>-1.878350292968889</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.1254</t>
+          <t>X &lt; 0.1251</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3512</v>
+        <v>3520</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.7646039737967598</v>
+        <v>-0.7976861243491911</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.7152576287060057</v>
+        <v>-0.7240929870530266</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.066493150703486</v>
+        <v>-1.074395915633104</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.261815883220287</v>
+        <v>-1.269324160259011</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9897973327994904</v>
+        <v>-0.9784407371143331</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9612002518618254</v>
+        <v>-0.9454885654436538</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.087503005661567</v>
+        <v>-1.10435046189513</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.169809065240855</v>
+        <v>-1.186312005004908</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.044843102961792</v>
+        <v>-1.066145952205851</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.139879794074126</v>
+        <v>-1.165209799199665</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.158259369389782</v>
+        <v>-1.18348715087437</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.364317561475836</v>
+        <v>-1.393639110325061</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.598056160508413</v>
+        <v>-1.631252807658932</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.499013943783346</v>
+        <v>-1.537074202647005</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.1431</t>
+          <t>X &lt; 0.1427</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3616</v>
+        <v>3627</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4555646940780278</v>
+        <v>-0.4496722644474218</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5364240640612437</v>
+        <v>-0.5346189457669439</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9440006106416163</v>
+        <v>-0.9411225553119138</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.157530879933084</v>
+        <v>-1.153953415295184</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8535586075157227</v>
+        <v>-0.8584932082157977</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.9275859632806558</v>
+        <v>-0.9284895604312808</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.025084073602585</v>
+        <v>-1.029419420455078</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.090811693045353</v>
+        <v>-1.095140745895392</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.9711645948875898</v>
+        <v>-0.9795789512373076</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.00499522534647</v>
+        <v>-1.017354794793469</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.8352682961187554</v>
+        <v>-0.8482325586590349</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.089604992656113</v>
+        <v>-1.105492438982836</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.107449801773399</v>
+        <v>-1.127165972550515</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.004628070821866</v>
+        <v>-1.028279681755706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.1608</t>
+          <t>X &lt; 0.1604</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3715</v>
+        <v>3722</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.415465386757532</v>
+        <v>-0.4083715303756037</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4833014796486168</v>
+        <v>-0.531424957177272</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.8368466699205825</v>
+        <v>-0.8572385243955765</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.9875208479863318</v>
+        <v>-1.007732353391525</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.8133052647993253</v>
+        <v>-0.8394233569798004</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7162853494126864</v>
+        <v>-0.7130166669434175</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8133865527038893</v>
+        <v>-0.8128627294023616</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9166097550246732</v>
+        <v>-0.9423700069962422</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.8017228972635166</v>
+        <v>-0.8306552736801578</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.8034543845988793</v>
+        <v>-0.8347558854494253</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.6974355887279415</v>
+        <v>-0.7287953556342686</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.8364317948838718</v>
+        <v>-0.8705651806725143</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.8649265300446558</v>
+        <v>-0.901705834862355</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.7049282173219424</v>
+        <v>-0.7451917836151978</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.1785</t>
+          <t>X &lt; 0.1781</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3781</v>
+        <v>3788</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2668938903129501</v>
+        <v>-0.2607037743739582</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2033597033503582</v>
+        <v>-0.1985520679375767</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4784346897878251</v>
+        <v>-0.4728126314452012</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.8087718150418297</v>
+        <v>-0.8026404874746191</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6205315854067237</v>
+        <v>-0.6193706654637623</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5199708557630771</v>
+        <v>-0.5430479966625725</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.5904051873015561</v>
+        <v>-0.6158172457081648</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7263167492134173</v>
+        <v>-0.7511232677354727</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5616192897451526</v>
+        <v>-0.5892166329858668</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.5780773976316738</v>
+        <v>-0.6075209914102686</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5038456366406692</v>
+        <v>-0.5332775361430393</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.5868978043049751</v>
+        <v>-0.6187435799311132</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6486024204302012</v>
+        <v>-0.6825507208921238</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.4609513734083919</v>
+        <v>-0.4979674540629517</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.1962</t>
+          <t>X &lt; 0.1957</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3847</v>
+        <v>3856</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.201123284420369</v>
+        <v>-0.1968525847732536</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1143876898070459</v>
+        <v>-0.137756335068687</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3137268002142903</v>
+        <v>-0.3365226314839944</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5842864254337741</v>
+        <v>-0.6064961939250679</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4602906149559942</v>
+        <v>-0.4867542231918023</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3563187520386961</v>
+        <v>-0.3810598954249187</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3750609625928334</v>
+        <v>-0.4018007512608293</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4646815883974966</v>
+        <v>-0.4910844536904619</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3816646116640854</v>
+        <v>-0.4103132112667325</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3604256150995937</v>
+        <v>-0.3909483323079428</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3168930543392534</v>
+        <v>-0.347467647896238</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.319940713377008</v>
+        <v>-0.3525934016359358</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4396989923305767</v>
+        <v>-0.4740271184960108</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3293230980928641</v>
+        <v>-0.3660538329751759</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.2139</t>
+          <t>X &lt; 0.2134</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3916</v>
+        <v>3923</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.05027210078123545</v>
+        <v>0.005132077552040926</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.05759237742014989</v>
+        <v>0.1125560708974405</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1706015450224356</v>
+        <v>-0.1148865831567321</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.357667213465831</v>
+        <v>-0.3525661981039576</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1433455611726586</v>
+        <v>-0.1922719574030225</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.08686052431109204</v>
+        <v>-0.08365481303316358</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1066943341600037</v>
+        <v>-0.105000481987318</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.04990382957515749</v>
+        <v>-0.07337097154182004</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.005181200604873482</v>
+        <v>-0.04541824352043022</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.01432547678407303</v>
+        <v>-0.04034648063934299</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1281754183136314</v>
+        <v>-0.1283584131376827</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.104992577447824</v>
+        <v>-0.1323479360139999</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2044578105741977</v>
+        <v>-0.2329150057243652</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.1430617262586082</v>
+        <v>-0.1734523223605819</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.2316</t>
+          <t>X &lt; 0.231</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3960</v>
+        <v>3969</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.02348870140625081</v>
+        <v>0.001189028955309368</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.187857594428003</v>
+        <v>0.1644352798591981</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.03339846344230324</v>
+        <v>0.01046053882839004</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1249103295003735</v>
+        <v>-0.1475424550317825</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.05593131872296908</v>
+        <v>0.03043052578657068</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1655409504842069</v>
+        <v>0.1410025224842641</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.09463525591143451</v>
+        <v>0.06895674739405422</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1204503512833952</v>
+        <v>0.09487322457446368</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1995110177726218</v>
+        <v>0.1724438888532305</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.09515474315455918</v>
+        <v>0.0672937655834005</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1064907785828098</v>
+        <v>0.07866897521861205</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1550969561226268</v>
+        <v>0.1258167516017821</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1026274115206931</v>
+        <v>0.07227914921443812</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.09016946202876142</v>
+        <v>0.05843016071450791</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.2492</t>
+          <t>X &lt; 0.2487</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4002</v>
+        <v>4012</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.002709305752283342</v>
+        <v>0.01162730554780467</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.2178131728642043</v>
+        <v>0.2307667559611417</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.08576541514540992</v>
+        <v>0.07424578372051371</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.06950978051759193</v>
+        <v>-0.08066349364210623</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1038155102122502</v>
+        <v>0.09019094147248552</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2403413486822714</v>
+        <v>0.2273885455997657</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.269085193765541</v>
+        <v>0.2550133707870685</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.2897788652086604</v>
+        <v>0.2757135312447616</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.3175012561669064</v>
+        <v>0.3023146858271915</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2552828658040838</v>
+        <v>0.2393026843508181</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2394245356862044</v>
+        <v>0.223505997512909</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.312889693420658</v>
+        <v>0.2957207027312805</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2815830710699032</v>
+        <v>0.2634839301499454</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.2966571272870482</v>
+        <v>0.3023507044498928</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.2669</t>
+          <t>X &lt; 0.2663</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4025</v>
+        <v>4035</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.07873673385282132</v>
+        <v>-0.08916320828618751</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2056437272811849</v>
+        <v>0.1938373563273217</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.09687277509574699</v>
+        <v>0.08539030381744084</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.03198913304242978</v>
+        <v>-0.04317499558538174</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1620774514998899</v>
+        <v>0.1486624034878048</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2995350455707211</v>
+        <v>0.2866458086291672</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2532416255242396</v>
+        <v>0.2395622706872089</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2711483019739234</v>
+        <v>0.2574894273638009</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2983598157224208</v>
+        <v>0.2837241411864753</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2812801072216828</v>
+        <v>0.2658922902747278</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2146975000914182</v>
+        <v>0.1994999330826488</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2631008927006562</v>
+        <v>0.2716286563032426</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2792375872617328</v>
+        <v>0.2868717453205178</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.3452042822809744</v>
+        <v>0.3517255044612497</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.2846</t>
+          <t>X &lt; 0.284</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4048</v>
+        <v>4059</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.006156119182463726</v>
+        <v>-0.005200233531390097</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1689816202441818</v>
+        <v>0.1685632147422353</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.009307817096399162</v>
+        <v>0.009287597956962657</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.06882184923997414</v>
+        <v>-0.06861987852403928</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1210837730440488</v>
+        <v>0.1191930559858534</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.210128419466848</v>
+        <v>0.2087884063892531</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1882559621261208</v>
+        <v>0.1861998023791642</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.2033951452287823</v>
+        <v>0.2012576846454763</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2300894599708698</v>
+        <v>0.2271052903250066</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2082655339538917</v>
+        <v>0.2044985094677756</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.140880719652742</v>
+        <v>0.1372771645974424</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2138775944085651</v>
+        <v>0.2093080522038946</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2769187500960086</v>
+        <v>0.2713708592068684</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.3190890931223009</v>
+        <v>0.3126732721004686</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.3023</t>
+          <t>X &lt; 0.3016</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4066</v>
+        <v>4077</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.0170768542656603</v>
+        <v>-0.0162242943246369</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1501735017083448</v>
+        <v>0.1498023103044375</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.06304064420994138</v>
+        <v>0.06287525428434293</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.01037813180040104</v>
+        <v>0.01036387150896445</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1970866220167551</v>
+        <v>0.1952134840393356</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2870703778521033</v>
+        <v>0.2856346467951383</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2158352541042348</v>
+        <v>0.213925482429147</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2288496431027696</v>
+        <v>0.2268701376840454</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.279726536576149</v>
+        <v>0.2769448008320481</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2542524703653015</v>
+        <v>0.2508162966499654</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1616954498083629</v>
+        <v>0.1584924453921772</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2345265619601946</v>
+        <v>0.230467353733232</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2708461028961011</v>
+        <v>0.2659953853799948</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.3138275878019812</v>
+        <v>0.308213664991861</v>
       </c>
     </row>
   </sheetData>
